--- a/연구코드/data/강남/강남_z_bounds.xlsx
+++ b/연구코드/data/강남/강남_z_bounds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="12">
   <si>
     <t>No</t>
   </si>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J446"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4762,6 +4762,9926 @@
         <v>10</v>
       </c>
     </row>
+    <row r="137" spans="1:10">
+      <c r="A137">
+        <v>1728</v>
+      </c>
+      <c r="B137">
+        <v>9722231</v>
+      </c>
+      <c r="C137">
+        <v>352</v>
+      </c>
+      <c r="D137">
+        <v>206</v>
+      </c>
+      <c r="E137">
+        <v>147</v>
+      </c>
+      <c r="F137">
+        <v>352</v>
+      </c>
+      <c r="G137">
+        <v>410</v>
+      </c>
+      <c r="H137">
+        <v>956.1</v>
+      </c>
+      <c r="I137">
+        <v>546.1</v>
+      </c>
+      <c r="J137" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138">
+        <v>1438</v>
+      </c>
+      <c r="B138">
+        <v>6739252</v>
+      </c>
+      <c r="C138">
+        <v>186</v>
+      </c>
+      <c r="D138">
+        <v>125</v>
+      </c>
+      <c r="E138">
+        <v>92</v>
+      </c>
+      <c r="F138">
+        <v>216</v>
+      </c>
+      <c r="G138">
+        <v>372</v>
+      </c>
+      <c r="H138">
+        <v>736.5</v>
+      </c>
+      <c r="I138">
+        <v>364.5</v>
+      </c>
+      <c r="J138" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139">
+        <v>1063</v>
+      </c>
+      <c r="B139">
+        <v>8974379</v>
+      </c>
+      <c r="C139">
+        <v>167</v>
+      </c>
+      <c r="D139">
+        <v>128</v>
+      </c>
+      <c r="E139">
+        <v>31</v>
+      </c>
+      <c r="F139">
+        <v>158</v>
+      </c>
+      <c r="G139">
+        <v>381</v>
+      </c>
+      <c r="H139">
+        <v>-292.6</v>
+      </c>
+      <c r="I139">
+        <v>-673.6</v>
+      </c>
+      <c r="J139" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140">
+        <v>1940</v>
+      </c>
+      <c r="B140">
+        <v>5606783</v>
+      </c>
+      <c r="C140">
+        <v>170</v>
+      </c>
+      <c r="D140">
+        <v>129</v>
+      </c>
+      <c r="E140">
+        <v>35</v>
+      </c>
+      <c r="F140">
+        <v>163</v>
+      </c>
+      <c r="G140">
+        <v>384</v>
+      </c>
+      <c r="H140">
+        <v>1025</v>
+      </c>
+      <c r="I140">
+        <v>641</v>
+      </c>
+      <c r="J140" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141">
+        <v>1004</v>
+      </c>
+      <c r="B141">
+        <v>8727149</v>
+      </c>
+      <c r="C141">
+        <v>194</v>
+      </c>
+      <c r="D141">
+        <v>194</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141">
+        <v>194</v>
+      </c>
+      <c r="G141">
+        <v>482.5</v>
+      </c>
+      <c r="H141">
+        <v>-180</v>
+      </c>
+      <c r="I141">
+        <v>-662.5</v>
+      </c>
+      <c r="J141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142">
+        <v>1216</v>
+      </c>
+      <c r="B142">
+        <v>6738001</v>
+      </c>
+      <c r="C142">
+        <v>191</v>
+      </c>
+      <c r="D142">
+        <v>187</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142">
+        <v>187</v>
+      </c>
+      <c r="G142">
+        <v>465</v>
+      </c>
+      <c r="H142">
+        <v>-373.191</v>
+      </c>
+      <c r="I142">
+        <v>-838.192</v>
+      </c>
+      <c r="J142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143">
+        <v>1041</v>
+      </c>
+      <c r="B143">
+        <v>8295847</v>
+      </c>
+      <c r="C143">
+        <v>160</v>
+      </c>
+      <c r="D143">
+        <v>115</v>
+      </c>
+      <c r="E143">
+        <v>27</v>
+      </c>
+      <c r="F143">
+        <v>141</v>
+      </c>
+      <c r="G143">
+        <v>342</v>
+      </c>
+      <c r="H143">
+        <v>32</v>
+      </c>
+      <c r="I143">
+        <v>-310</v>
+      </c>
+      <c r="J143" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144">
+        <v>834</v>
+      </c>
+      <c r="B144">
+        <v>8781000</v>
+      </c>
+      <c r="C144">
+        <v>150</v>
+      </c>
+      <c r="D144">
+        <v>124</v>
+      </c>
+      <c r="E144">
+        <v>20</v>
+      </c>
+      <c r="F144">
+        <v>143</v>
+      </c>
+      <c r="G144">
+        <v>369</v>
+      </c>
+      <c r="H144">
+        <v>21.49</v>
+      </c>
+      <c r="I144">
+        <v>-347.51</v>
+      </c>
+      <c r="J144" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145">
+        <v>1677</v>
+      </c>
+      <c r="B145">
+        <v>9632636</v>
+      </c>
+      <c r="C145">
+        <v>289</v>
+      </c>
+      <c r="D145">
+        <v>189</v>
+      </c>
+      <c r="E145">
+        <v>84</v>
+      </c>
+      <c r="F145">
+        <v>272</v>
+      </c>
+      <c r="G145">
+        <v>376</v>
+      </c>
+      <c r="H145">
+        <v>1080</v>
+      </c>
+      <c r="I145">
+        <v>704</v>
+      </c>
+      <c r="J145" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146">
+        <v>178</v>
+      </c>
+      <c r="B146">
+        <v>5727873</v>
+      </c>
+      <c r="C146">
+        <v>175</v>
+      </c>
+      <c r="D146">
+        <v>132</v>
+      </c>
+      <c r="E146">
+        <v>21</v>
+      </c>
+      <c r="F146">
+        <v>152</v>
+      </c>
+      <c r="G146">
+        <v>393</v>
+      </c>
+      <c r="H146">
+        <v>-211.9</v>
+      </c>
+      <c r="I146">
+        <v>-604.9</v>
+      </c>
+      <c r="J146" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147">
+        <v>1403</v>
+      </c>
+      <c r="B147">
+        <v>9515861</v>
+      </c>
+      <c r="C147">
+        <v>161</v>
+      </c>
+      <c r="D147">
+        <v>121</v>
+      </c>
+      <c r="E147">
+        <v>31</v>
+      </c>
+      <c r="F147">
+        <v>151</v>
+      </c>
+      <c r="G147">
+        <v>360</v>
+      </c>
+      <c r="H147">
+        <v>168.5</v>
+      </c>
+      <c r="I147">
+        <v>-191.5</v>
+      </c>
+      <c r="J147" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148">
+        <v>599</v>
+      </c>
+      <c r="B148">
+        <v>5216965</v>
+      </c>
+      <c r="C148">
+        <v>157</v>
+      </c>
+      <c r="D148">
+        <v>113</v>
+      </c>
+      <c r="E148">
+        <v>37</v>
+      </c>
+      <c r="F148">
+        <v>149</v>
+      </c>
+      <c r="G148">
+        <v>336</v>
+      </c>
+      <c r="H148">
+        <v>785.4</v>
+      </c>
+      <c r="I148">
+        <v>449.4</v>
+      </c>
+      <c r="J148" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149">
+        <v>1096</v>
+      </c>
+      <c r="B149">
+        <v>8907310</v>
+      </c>
+      <c r="C149">
+        <v>155</v>
+      </c>
+      <c r="D149">
+        <v>122</v>
+      </c>
+      <c r="E149">
+        <v>25</v>
+      </c>
+      <c r="F149">
+        <v>146</v>
+      </c>
+      <c r="G149">
+        <v>363</v>
+      </c>
+      <c r="H149">
+        <v>-147.9</v>
+      </c>
+      <c r="I149">
+        <v>-510.9</v>
+      </c>
+      <c r="J149" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150">
+        <v>1515</v>
+      </c>
+      <c r="B150">
+        <v>9002483</v>
+      </c>
+      <c r="C150">
+        <v>180</v>
+      </c>
+      <c r="D150">
+        <v>130</v>
+      </c>
+      <c r="E150">
+        <v>43</v>
+      </c>
+      <c r="F150">
+        <v>172</v>
+      </c>
+      <c r="G150">
+        <v>387</v>
+      </c>
+      <c r="H150">
+        <v>168.4</v>
+      </c>
+      <c r="I150">
+        <v>-218.6</v>
+      </c>
+      <c r="J150" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151">
+        <v>774</v>
+      </c>
+      <c r="B151">
+        <v>2817512</v>
+      </c>
+      <c r="C151">
+        <v>195</v>
+      </c>
+      <c r="D151">
+        <v>146</v>
+      </c>
+      <c r="E151">
+        <v>34</v>
+      </c>
+      <c r="F151">
+        <v>179</v>
+      </c>
+      <c r="G151">
+        <v>362.5</v>
+      </c>
+      <c r="H151">
+        <v>-297.614</v>
+      </c>
+      <c r="I151">
+        <v>-660.114</v>
+      </c>
+      <c r="J151" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152">
+        <v>6</v>
+      </c>
+      <c r="B152">
+        <v>5242623</v>
+      </c>
+      <c r="C152">
+        <v>147</v>
+      </c>
+      <c r="D152">
+        <v>121</v>
+      </c>
+      <c r="E152">
+        <v>90</v>
+      </c>
+      <c r="F152">
+        <v>210</v>
+      </c>
+      <c r="G152">
+        <v>360</v>
+      </c>
+      <c r="H152">
+        <v>1561.5</v>
+      </c>
+      <c r="I152">
+        <v>1201.5</v>
+      </c>
+      <c r="J152" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153">
+        <v>305</v>
+      </c>
+      <c r="B153">
+        <v>5833204</v>
+      </c>
+      <c r="C153">
+        <v>179</v>
+      </c>
+      <c r="D153">
+        <v>172</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+      <c r="F153">
+        <v>172</v>
+      </c>
+      <c r="G153">
+        <v>427.5</v>
+      </c>
+      <c r="H153">
+        <v>-85</v>
+      </c>
+      <c r="I153">
+        <v>-512.5</v>
+      </c>
+      <c r="J153" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154">
+        <v>1528</v>
+      </c>
+      <c r="B154">
+        <v>9002440</v>
+      </c>
+      <c r="C154">
+        <v>184</v>
+      </c>
+      <c r="D154">
+        <v>170</v>
+      </c>
+      <c r="E154">
+        <v>1</v>
+      </c>
+      <c r="F154">
+        <v>170</v>
+      </c>
+      <c r="G154">
+        <v>422.5</v>
+      </c>
+      <c r="H154">
+        <v>-190</v>
+      </c>
+      <c r="I154">
+        <v>-612.5</v>
+      </c>
+      <c r="J154" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155">
+        <v>1231</v>
+      </c>
+      <c r="B155">
+        <v>8541260</v>
+      </c>
+      <c r="C155">
+        <v>170</v>
+      </c>
+      <c r="D155">
+        <v>112</v>
+      </c>
+      <c r="E155">
+        <v>42</v>
+      </c>
+      <c r="F155">
+        <v>153</v>
+      </c>
+      <c r="G155">
+        <v>333</v>
+      </c>
+      <c r="H155">
+        <v>-506.2</v>
+      </c>
+      <c r="I155">
+        <v>-839.2</v>
+      </c>
+      <c r="J155" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="A156">
+        <v>1582</v>
+      </c>
+      <c r="B156">
+        <v>9466854</v>
+      </c>
+      <c r="C156">
+        <v>237</v>
+      </c>
+      <c r="D156">
+        <v>184</v>
+      </c>
+      <c r="E156">
+        <v>54</v>
+      </c>
+      <c r="F156">
+        <v>237</v>
+      </c>
+      <c r="G156">
+        <v>366</v>
+      </c>
+      <c r="H156">
+        <v>-97</v>
+      </c>
+      <c r="I156">
+        <v>-463</v>
+      </c>
+      <c r="J156" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="A157">
+        <v>942</v>
+      </c>
+      <c r="B157">
+        <v>6741744</v>
+      </c>
+      <c r="C157">
+        <v>183</v>
+      </c>
+      <c r="D157">
+        <v>135</v>
+      </c>
+      <c r="E157">
+        <v>39</v>
+      </c>
+      <c r="F157">
+        <v>173</v>
+      </c>
+      <c r="G157">
+        <v>402</v>
+      </c>
+      <c r="H157">
+        <v>178.1</v>
+      </c>
+      <c r="I157">
+        <v>-223.9</v>
+      </c>
+      <c r="J157" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158">
+        <v>78</v>
+      </c>
+      <c r="B158">
+        <v>5025808</v>
+      </c>
+      <c r="C158">
+        <v>181</v>
+      </c>
+      <c r="D158">
+        <v>125</v>
+      </c>
+      <c r="E158">
+        <v>34</v>
+      </c>
+      <c r="F158">
+        <v>158</v>
+      </c>
+      <c r="G158">
+        <v>372</v>
+      </c>
+      <c r="H158">
+        <v>-142</v>
+      </c>
+      <c r="I158">
+        <v>-514</v>
+      </c>
+      <c r="J158" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="A159">
+        <v>142</v>
+      </c>
+      <c r="B159">
+        <v>5360671</v>
+      </c>
+      <c r="C159">
+        <v>175</v>
+      </c>
+      <c r="D159">
+        <v>127</v>
+      </c>
+      <c r="E159">
+        <v>90</v>
+      </c>
+      <c r="F159">
+        <v>216</v>
+      </c>
+      <c r="G159">
+        <v>378</v>
+      </c>
+      <c r="H159">
+        <v>1071.5</v>
+      </c>
+      <c r="I159">
+        <v>693.5</v>
+      </c>
+      <c r="J159" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="A160">
+        <v>794</v>
+      </c>
+      <c r="B160">
+        <v>8879875</v>
+      </c>
+      <c r="C160">
+        <v>167</v>
+      </c>
+      <c r="D160">
+        <v>128</v>
+      </c>
+      <c r="E160">
+        <v>34</v>
+      </c>
+      <c r="F160">
+        <v>161</v>
+      </c>
+      <c r="G160">
+        <v>381</v>
+      </c>
+      <c r="H160">
+        <v>-273.4</v>
+      </c>
+      <c r="I160">
+        <v>-654.4</v>
+      </c>
+      <c r="J160" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161">
+        <v>1281</v>
+      </c>
+      <c r="B161">
+        <v>6738709</v>
+      </c>
+      <c r="C161">
+        <v>203</v>
+      </c>
+      <c r="D161">
+        <v>191</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+      <c r="F161">
+        <v>191</v>
+      </c>
+      <c r="G161">
+        <v>475</v>
+      </c>
+      <c r="H161">
+        <v>-187.5</v>
+      </c>
+      <c r="I161">
+        <v>-662.5</v>
+      </c>
+      <c r="J161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162">
+        <v>1590</v>
+      </c>
+      <c r="B162">
+        <v>9485957</v>
+      </c>
+      <c r="C162">
+        <v>159</v>
+      </c>
+      <c r="D162">
+        <v>124</v>
+      </c>
+      <c r="E162">
+        <v>26</v>
+      </c>
+      <c r="F162">
+        <v>149</v>
+      </c>
+      <c r="G162">
+        <v>369</v>
+      </c>
+      <c r="H162">
+        <v>650.4</v>
+      </c>
+      <c r="I162">
+        <v>281.4</v>
+      </c>
+      <c r="J162" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163">
+        <v>997</v>
+      </c>
+      <c r="B163">
+        <v>8364628</v>
+      </c>
+      <c r="C163">
+        <v>165</v>
+      </c>
+      <c r="D163">
+        <v>135</v>
+      </c>
+      <c r="E163">
+        <v>19</v>
+      </c>
+      <c r="F163">
+        <v>153</v>
+      </c>
+      <c r="G163">
+        <v>402</v>
+      </c>
+      <c r="H163">
+        <v>689.5</v>
+      </c>
+      <c r="I163">
+        <v>287.5</v>
+      </c>
+      <c r="J163" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164">
+        <v>1724</v>
+      </c>
+      <c r="B164">
+        <v>9713380</v>
+      </c>
+      <c r="C164">
+        <v>172</v>
+      </c>
+      <c r="D164">
+        <v>121</v>
+      </c>
+      <c r="E164">
+        <v>40</v>
+      </c>
+      <c r="F164">
+        <v>160</v>
+      </c>
+      <c r="G164">
+        <v>360</v>
+      </c>
+      <c r="H164">
+        <v>1660.5</v>
+      </c>
+      <c r="I164">
+        <v>1300.5</v>
+      </c>
+      <c r="J164" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="A165">
+        <v>48</v>
+      </c>
+      <c r="B165">
+        <v>1352435</v>
+      </c>
+      <c r="C165">
+        <v>165</v>
+      </c>
+      <c r="D165">
+        <v>129</v>
+      </c>
+      <c r="E165">
+        <v>29</v>
+      </c>
+      <c r="F165">
+        <v>157</v>
+      </c>
+      <c r="G165">
+        <v>384</v>
+      </c>
+      <c r="H165">
+        <v>-152</v>
+      </c>
+      <c r="I165">
+        <v>-536</v>
+      </c>
+      <c r="J165" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="A166">
+        <v>845</v>
+      </c>
+      <c r="B166">
+        <v>8933611</v>
+      </c>
+      <c r="C166">
+        <v>203</v>
+      </c>
+      <c r="D166">
+        <v>196</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+      <c r="F166">
+        <v>196</v>
+      </c>
+      <c r="G166">
+        <v>487.5</v>
+      </c>
+      <c r="H166">
+        <v>-167.5</v>
+      </c>
+      <c r="I166">
+        <v>-655</v>
+      </c>
+      <c r="J166" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="A167">
+        <v>898</v>
+      </c>
+      <c r="B167">
+        <v>8415113</v>
+      </c>
+      <c r="C167">
+        <v>175</v>
+      </c>
+      <c r="D167">
+        <v>128</v>
+      </c>
+      <c r="E167">
+        <v>95</v>
+      </c>
+      <c r="F167">
+        <v>222</v>
+      </c>
+      <c r="G167">
+        <v>381</v>
+      </c>
+      <c r="H167">
+        <v>1607</v>
+      </c>
+      <c r="I167">
+        <v>1226</v>
+      </c>
+      <c r="J167" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="A168">
+        <v>100</v>
+      </c>
+      <c r="B168">
+        <v>5158026</v>
+      </c>
+      <c r="C168">
+        <v>172</v>
+      </c>
+      <c r="D168">
+        <v>128</v>
+      </c>
+      <c r="E168">
+        <v>39</v>
+      </c>
+      <c r="F168">
+        <v>166</v>
+      </c>
+      <c r="G168">
+        <v>381</v>
+      </c>
+      <c r="H168">
+        <v>919.4</v>
+      </c>
+      <c r="I168">
+        <v>538.4</v>
+      </c>
+      <c r="J168" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="A169">
+        <v>987</v>
+      </c>
+      <c r="B169">
+        <v>8869645</v>
+      </c>
+      <c r="C169">
+        <v>249</v>
+      </c>
+      <c r="D169">
+        <v>199</v>
+      </c>
+      <c r="E169">
+        <v>45</v>
+      </c>
+      <c r="F169">
+        <v>243</v>
+      </c>
+      <c r="G169">
+        <v>396</v>
+      </c>
+      <c r="H169">
+        <v>910.4</v>
+      </c>
+      <c r="I169">
+        <v>514.4</v>
+      </c>
+      <c r="J169" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="A170">
+        <v>1217</v>
+      </c>
+      <c r="B170">
+        <v>8957014</v>
+      </c>
+      <c r="C170">
+        <v>171</v>
+      </c>
+      <c r="D170">
+        <v>129</v>
+      </c>
+      <c r="E170">
+        <v>93</v>
+      </c>
+      <c r="F170">
+        <v>221</v>
+      </c>
+      <c r="G170">
+        <v>384</v>
+      </c>
+      <c r="H170">
+        <v>-235.6</v>
+      </c>
+      <c r="I170">
+        <v>-619.6</v>
+      </c>
+      <c r="J170" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="A171">
+        <v>87</v>
+      </c>
+      <c r="B171">
+        <v>5553660</v>
+      </c>
+      <c r="C171">
+        <v>175</v>
+      </c>
+      <c r="D171">
+        <v>135</v>
+      </c>
+      <c r="E171">
+        <v>34</v>
+      </c>
+      <c r="F171">
+        <v>168</v>
+      </c>
+      <c r="G171">
+        <v>402</v>
+      </c>
+      <c r="H171">
+        <v>1502.5</v>
+      </c>
+      <c r="I171">
+        <v>1100.5</v>
+      </c>
+      <c r="J171" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="A172">
+        <v>517</v>
+      </c>
+      <c r="B172">
+        <v>2960118</v>
+      </c>
+      <c r="C172">
+        <v>196</v>
+      </c>
+      <c r="D172">
+        <v>186</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+      <c r="F172">
+        <v>186</v>
+      </c>
+      <c r="G172">
+        <v>462.5</v>
+      </c>
+      <c r="H172">
+        <v>-137.5</v>
+      </c>
+      <c r="I172">
+        <v>-600</v>
+      </c>
+      <c r="J172" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="A173">
+        <v>525</v>
+      </c>
+      <c r="B173">
+        <v>2196059</v>
+      </c>
+      <c r="C173">
+        <v>181</v>
+      </c>
+      <c r="D173">
+        <v>128</v>
+      </c>
+      <c r="E173">
+        <v>31</v>
+      </c>
+      <c r="F173">
+        <v>158</v>
+      </c>
+      <c r="G173">
+        <v>381</v>
+      </c>
+      <c r="H173">
+        <v>-170.4</v>
+      </c>
+      <c r="I173">
+        <v>-551.4</v>
+      </c>
+      <c r="J173" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="A174">
+        <v>1783</v>
+      </c>
+      <c r="B174">
+        <v>9811101</v>
+      </c>
+      <c r="C174">
+        <v>198</v>
+      </c>
+      <c r="D174">
+        <v>174</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="F174">
+        <v>174</v>
+      </c>
+      <c r="G174">
+        <v>432.5</v>
+      </c>
+      <c r="H174">
+        <v>-209.738</v>
+      </c>
+      <c r="I174">
+        <v>-642.237</v>
+      </c>
+      <c r="J174" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="A175">
+        <v>956</v>
+      </c>
+      <c r="B175">
+        <v>8961399</v>
+      </c>
+      <c r="C175">
+        <v>196</v>
+      </c>
+      <c r="D175">
+        <v>188</v>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+      <c r="F175">
+        <v>188</v>
+      </c>
+      <c r="G175">
+        <v>467.5</v>
+      </c>
+      <c r="H175">
+        <v>-250</v>
+      </c>
+      <c r="I175">
+        <v>-717.5</v>
+      </c>
+      <c r="J175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="A176">
+        <v>1095</v>
+      </c>
+      <c r="B176">
+        <v>8912422</v>
+      </c>
+      <c r="C176">
+        <v>178</v>
+      </c>
+      <c r="D176">
+        <v>128</v>
+      </c>
+      <c r="E176">
+        <v>34</v>
+      </c>
+      <c r="F176">
+        <v>161</v>
+      </c>
+      <c r="G176">
+        <v>381</v>
+      </c>
+      <c r="H176">
+        <v>1508.5</v>
+      </c>
+      <c r="I176">
+        <v>1127.5</v>
+      </c>
+      <c r="J176" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="A177">
+        <v>1156</v>
+      </c>
+      <c r="B177">
+        <v>6715946</v>
+      </c>
+      <c r="C177">
+        <v>161</v>
+      </c>
+      <c r="D177">
+        <v>130</v>
+      </c>
+      <c r="E177">
+        <v>86</v>
+      </c>
+      <c r="F177">
+        <v>215</v>
+      </c>
+      <c r="G177">
+        <v>387</v>
+      </c>
+      <c r="H177">
+        <v>1553</v>
+      </c>
+      <c r="I177">
+        <v>1166</v>
+      </c>
+      <c r="J177" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="A178">
+        <v>1794</v>
+      </c>
+      <c r="B178">
+        <v>9832208</v>
+      </c>
+      <c r="C178">
+        <v>203</v>
+      </c>
+      <c r="D178">
+        <v>189</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+      <c r="F178">
+        <v>189</v>
+      </c>
+      <c r="G178">
+        <v>470</v>
+      </c>
+      <c r="H178">
+        <v>-172.417</v>
+      </c>
+      <c r="I178">
+        <v>-642.417</v>
+      </c>
+      <c r="J178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="A179">
+        <v>225</v>
+      </c>
+      <c r="B179">
+        <v>5264302</v>
+      </c>
+      <c r="C179">
+        <v>195</v>
+      </c>
+      <c r="D179">
+        <v>131</v>
+      </c>
+      <c r="E179">
+        <v>30</v>
+      </c>
+      <c r="F179">
+        <v>160</v>
+      </c>
+      <c r="G179">
+        <v>390</v>
+      </c>
+      <c r="H179">
+        <v>1101</v>
+      </c>
+      <c r="I179">
+        <v>711</v>
+      </c>
+      <c r="J179" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="A180">
+        <v>1530</v>
+      </c>
+      <c r="B180">
+        <v>9003856</v>
+      </c>
+      <c r="C180">
+        <v>192</v>
+      </c>
+      <c r="D180">
+        <v>185</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+      <c r="F180">
+        <v>185</v>
+      </c>
+      <c r="G180">
+        <v>460</v>
+      </c>
+      <c r="H180">
+        <v>-185</v>
+      </c>
+      <c r="I180">
+        <v>-645</v>
+      </c>
+      <c r="J180" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181">
+        <v>1215</v>
+      </c>
+      <c r="B181">
+        <v>8578293</v>
+      </c>
+      <c r="C181">
+        <v>162</v>
+      </c>
+      <c r="D181">
+        <v>129</v>
+      </c>
+      <c r="E181">
+        <v>92</v>
+      </c>
+      <c r="F181">
+        <v>220</v>
+      </c>
+      <c r="G181">
+        <v>384</v>
+      </c>
+      <c r="H181">
+        <v>-287</v>
+      </c>
+      <c r="I181">
+        <v>-671</v>
+      </c>
+      <c r="J181" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182">
+        <v>1244</v>
+      </c>
+      <c r="B182">
+        <v>6742595</v>
+      </c>
+      <c r="C182">
+        <v>145</v>
+      </c>
+      <c r="D182">
+        <v>123</v>
+      </c>
+      <c r="E182">
+        <v>22</v>
+      </c>
+      <c r="F182">
+        <v>144</v>
+      </c>
+      <c r="G182">
+        <v>366</v>
+      </c>
+      <c r="H182">
+        <v>-183.49</v>
+      </c>
+      <c r="I182">
+        <v>-549.49</v>
+      </c>
+      <c r="J182" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="A183">
+        <v>434</v>
+      </c>
+      <c r="B183">
+        <v>2198986</v>
+      </c>
+      <c r="C183">
+        <v>155</v>
+      </c>
+      <c r="D183">
+        <v>129</v>
+      </c>
+      <c r="E183">
+        <v>16</v>
+      </c>
+      <c r="F183">
+        <v>144</v>
+      </c>
+      <c r="G183">
+        <v>384</v>
+      </c>
+      <c r="H183">
+        <v>909.4</v>
+      </c>
+      <c r="I183">
+        <v>525.4</v>
+      </c>
+      <c r="J183" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="A184">
+        <v>215</v>
+      </c>
+      <c r="B184">
+        <v>5024821</v>
+      </c>
+      <c r="C184">
+        <v>186</v>
+      </c>
+      <c r="D184">
+        <v>175</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184">
+        <v>175</v>
+      </c>
+      <c r="G184">
+        <v>435</v>
+      </c>
+      <c r="H184">
+        <v>-192.5</v>
+      </c>
+      <c r="I184">
+        <v>-627.5</v>
+      </c>
+      <c r="J184" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185">
+        <v>174</v>
+      </c>
+      <c r="B185">
+        <v>5657695</v>
+      </c>
+      <c r="C185">
+        <v>166</v>
+      </c>
+      <c r="D185">
+        <v>129</v>
+      </c>
+      <c r="E185">
+        <v>30</v>
+      </c>
+      <c r="F185">
+        <v>158</v>
+      </c>
+      <c r="G185">
+        <v>384</v>
+      </c>
+      <c r="H185">
+        <v>639.3</v>
+      </c>
+      <c r="I185">
+        <v>255.3</v>
+      </c>
+      <c r="J185" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186">
+        <v>1604</v>
+      </c>
+      <c r="B186">
+        <v>9503421</v>
+      </c>
+      <c r="C186">
+        <v>157</v>
+      </c>
+      <c r="D186">
+        <v>121</v>
+      </c>
+      <c r="E186">
+        <v>18</v>
+      </c>
+      <c r="F186">
+        <v>138</v>
+      </c>
+      <c r="G186">
+        <v>360</v>
+      </c>
+      <c r="H186">
+        <v>740.5</v>
+      </c>
+      <c r="I186">
+        <v>380.5</v>
+      </c>
+      <c r="J186" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="A187">
+        <v>1302</v>
+      </c>
+      <c r="B187">
+        <v>8801204</v>
+      </c>
+      <c r="C187">
+        <v>169</v>
+      </c>
+      <c r="D187">
+        <v>131</v>
+      </c>
+      <c r="E187">
+        <v>29</v>
+      </c>
+      <c r="F187">
+        <v>159</v>
+      </c>
+      <c r="G187">
+        <v>390</v>
+      </c>
+      <c r="H187">
+        <v>-348</v>
+      </c>
+      <c r="I187">
+        <v>-738</v>
+      </c>
+      <c r="J187" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="A188">
+        <v>553</v>
+      </c>
+      <c r="B188">
+        <v>2538674</v>
+      </c>
+      <c r="C188">
+        <v>152</v>
+      </c>
+      <c r="D188">
+        <v>131</v>
+      </c>
+      <c r="E188">
+        <v>90</v>
+      </c>
+      <c r="F188">
+        <v>220</v>
+      </c>
+      <c r="G188">
+        <v>390</v>
+      </c>
+      <c r="H188">
+        <v>844.5</v>
+      </c>
+      <c r="I188">
+        <v>454.5</v>
+      </c>
+      <c r="J188" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="A189">
+        <v>1508</v>
+      </c>
+      <c r="B189">
+        <v>6740770</v>
+      </c>
+      <c r="C189">
+        <v>200</v>
+      </c>
+      <c r="D189">
+        <v>181</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+      <c r="F189">
+        <v>181</v>
+      </c>
+      <c r="G189">
+        <v>450</v>
+      </c>
+      <c r="H189">
+        <v>-175</v>
+      </c>
+      <c r="I189">
+        <v>-625</v>
+      </c>
+      <c r="J189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="A190">
+        <v>351</v>
+      </c>
+      <c r="B190">
+        <v>3375617</v>
+      </c>
+      <c r="C190">
+        <v>186</v>
+      </c>
+      <c r="D190">
+        <v>177</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+      <c r="F190">
+        <v>177</v>
+      </c>
+      <c r="G190">
+        <v>440</v>
+      </c>
+      <c r="H190">
+        <v>-210</v>
+      </c>
+      <c r="I190">
+        <v>-650</v>
+      </c>
+      <c r="J190" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="A191">
+        <v>1845</v>
+      </c>
+      <c r="B191">
+        <v>9912449</v>
+      </c>
+      <c r="C191">
+        <v>204</v>
+      </c>
+      <c r="D191">
+        <v>154</v>
+      </c>
+      <c r="E191">
+        <v>37</v>
+      </c>
+      <c r="F191">
+        <v>190</v>
+      </c>
+      <c r="G191">
+        <v>382.5</v>
+      </c>
+      <c r="H191">
+        <v>-267.734</v>
+      </c>
+      <c r="I191">
+        <v>-650.234</v>
+      </c>
+      <c r="J191" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192">
+        <v>887</v>
+      </c>
+      <c r="B192">
+        <v>8796993</v>
+      </c>
+      <c r="C192">
+        <v>175</v>
+      </c>
+      <c r="D192">
+        <v>125</v>
+      </c>
+      <c r="E192">
+        <v>30</v>
+      </c>
+      <c r="F192">
+        <v>154</v>
+      </c>
+      <c r="G192">
+        <v>372</v>
+      </c>
+      <c r="H192">
+        <v>820</v>
+      </c>
+      <c r="I192">
+        <v>448</v>
+      </c>
+      <c r="J192" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193">
+        <v>1699</v>
+      </c>
+      <c r="B193">
+        <v>9666989</v>
+      </c>
+      <c r="C193">
+        <v>171</v>
+      </c>
+      <c r="D193">
+        <v>126</v>
+      </c>
+      <c r="E193">
+        <v>30</v>
+      </c>
+      <c r="F193">
+        <v>155</v>
+      </c>
+      <c r="G193">
+        <v>375</v>
+      </c>
+      <c r="H193">
+        <v>808.5</v>
+      </c>
+      <c r="I193">
+        <v>433.5</v>
+      </c>
+      <c r="J193" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194">
+        <v>609</v>
+      </c>
+      <c r="B194">
+        <v>5023526</v>
+      </c>
+      <c r="C194">
+        <v>186</v>
+      </c>
+      <c r="D194">
+        <v>174</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194">
+        <v>174</v>
+      </c>
+      <c r="G194">
+        <v>432.5</v>
+      </c>
+      <c r="H194">
+        <v>-225</v>
+      </c>
+      <c r="I194">
+        <v>-657.5</v>
+      </c>
+      <c r="J194" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195">
+        <v>968</v>
+      </c>
+      <c r="B195">
+        <v>8976485</v>
+      </c>
+      <c r="C195">
+        <v>156</v>
+      </c>
+      <c r="D195">
+        <v>119</v>
+      </c>
+      <c r="E195">
+        <v>25</v>
+      </c>
+      <c r="F195">
+        <v>143</v>
+      </c>
+      <c r="G195">
+        <v>354</v>
+      </c>
+      <c r="H195">
+        <v>1692.5</v>
+      </c>
+      <c r="I195">
+        <v>1338.5</v>
+      </c>
+      <c r="J195" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196">
+        <v>530</v>
+      </c>
+      <c r="B196">
+        <v>4681481</v>
+      </c>
+      <c r="C196">
+        <v>170</v>
+      </c>
+      <c r="D196">
+        <v>118</v>
+      </c>
+      <c r="E196">
+        <v>86</v>
+      </c>
+      <c r="F196">
+        <v>203</v>
+      </c>
+      <c r="G196">
+        <v>351</v>
+      </c>
+      <c r="H196">
+        <v>-251</v>
+      </c>
+      <c r="I196">
+        <v>-602</v>
+      </c>
+      <c r="J196" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197">
+        <v>1949</v>
+      </c>
+      <c r="B197">
+        <v>4291924</v>
+      </c>
+      <c r="C197">
+        <v>173</v>
+      </c>
+      <c r="D197">
+        <v>115</v>
+      </c>
+      <c r="E197">
+        <v>40</v>
+      </c>
+      <c r="F197">
+        <v>154</v>
+      </c>
+      <c r="G197">
+        <v>342</v>
+      </c>
+      <c r="H197">
+        <v>1056.4</v>
+      </c>
+      <c r="I197">
+        <v>714.4</v>
+      </c>
+      <c r="J197" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198">
+        <v>271</v>
+      </c>
+      <c r="B198">
+        <v>5651763</v>
+      </c>
+      <c r="C198">
+        <v>169</v>
+      </c>
+      <c r="D198">
+        <v>125</v>
+      </c>
+      <c r="E198">
+        <v>32</v>
+      </c>
+      <c r="F198">
+        <v>156</v>
+      </c>
+      <c r="G198">
+        <v>372</v>
+      </c>
+      <c r="H198">
+        <v>-329.31</v>
+      </c>
+      <c r="I198">
+        <v>-701.3099999999999</v>
+      </c>
+      <c r="J198" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="A199">
+        <v>1759</v>
+      </c>
+      <c r="B199">
+        <v>9764072</v>
+      </c>
+      <c r="C199">
+        <v>181</v>
+      </c>
+      <c r="D199">
+        <v>132</v>
+      </c>
+      <c r="E199">
+        <v>36</v>
+      </c>
+      <c r="F199">
+        <v>167</v>
+      </c>
+      <c r="G199">
+        <v>393</v>
+      </c>
+      <c r="H199">
+        <v>952.8</v>
+      </c>
+      <c r="I199">
+        <v>559.8</v>
+      </c>
+      <c r="J199" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="A200">
+        <v>1752</v>
+      </c>
+      <c r="B200">
+        <v>9756117</v>
+      </c>
+      <c r="C200">
+        <v>147</v>
+      </c>
+      <c r="D200">
+        <v>122</v>
+      </c>
+      <c r="E200">
+        <v>26</v>
+      </c>
+      <c r="F200">
+        <v>147</v>
+      </c>
+      <c r="G200">
+        <v>363</v>
+      </c>
+      <c r="H200">
+        <v>497.5</v>
+      </c>
+      <c r="I200">
+        <v>134.5</v>
+      </c>
+      <c r="J200" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
+      <c r="A201">
+        <v>1490</v>
+      </c>
+      <c r="B201">
+        <v>6740037</v>
+      </c>
+      <c r="C201">
+        <v>196</v>
+      </c>
+      <c r="D201">
+        <v>177</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+      <c r="F201">
+        <v>177</v>
+      </c>
+      <c r="G201">
+        <v>440</v>
+      </c>
+      <c r="H201">
+        <v>-285</v>
+      </c>
+      <c r="I201">
+        <v>-725</v>
+      </c>
+      <c r="J201" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
+      <c r="A202">
+        <v>1588</v>
+      </c>
+      <c r="B202">
+        <v>9476121</v>
+      </c>
+      <c r="C202">
+        <v>197</v>
+      </c>
+      <c r="D202">
+        <v>178</v>
+      </c>
+      <c r="E202">
+        <v>1</v>
+      </c>
+      <c r="F202">
+        <v>178</v>
+      </c>
+      <c r="G202">
+        <v>442.5</v>
+      </c>
+      <c r="H202">
+        <v>-197.5</v>
+      </c>
+      <c r="I202">
+        <v>-640</v>
+      </c>
+      <c r="J202" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10">
+      <c r="A203">
+        <v>1320</v>
+      </c>
+      <c r="B203">
+        <v>1523339</v>
+      </c>
+      <c r="C203">
+        <v>173</v>
+      </c>
+      <c r="D203">
+        <v>124</v>
+      </c>
+      <c r="E203">
+        <v>40</v>
+      </c>
+      <c r="F203">
+        <v>163</v>
+      </c>
+      <c r="G203">
+        <v>369</v>
+      </c>
+      <c r="H203">
+        <v>1603</v>
+      </c>
+      <c r="I203">
+        <v>1234</v>
+      </c>
+      <c r="J203" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10">
+      <c r="A204">
+        <v>678</v>
+      </c>
+      <c r="B204">
+        <v>6089611</v>
+      </c>
+      <c r="C204">
+        <v>131</v>
+      </c>
+      <c r="D204">
+        <v>126</v>
+      </c>
+      <c r="E204">
+        <v>6</v>
+      </c>
+      <c r="F204">
+        <v>131</v>
+      </c>
+      <c r="G204">
+        <v>375.01</v>
+      </c>
+      <c r="H204">
+        <v>837.35</v>
+      </c>
+      <c r="I204">
+        <v>462.34</v>
+      </c>
+      <c r="J204" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10">
+      <c r="A205">
+        <v>1074</v>
+      </c>
+      <c r="B205">
+        <v>6738330</v>
+      </c>
+      <c r="C205">
+        <v>187</v>
+      </c>
+      <c r="D205">
+        <v>164</v>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+      <c r="F205">
+        <v>164</v>
+      </c>
+      <c r="G205">
+        <v>407.5</v>
+      </c>
+      <c r="H205">
+        <v>-166.471</v>
+      </c>
+      <c r="I205">
+        <v>-573.971</v>
+      </c>
+      <c r="J205" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10">
+      <c r="A206">
+        <v>1492</v>
+      </c>
+      <c r="B206">
+        <v>6743363</v>
+      </c>
+      <c r="C206">
+        <v>127</v>
+      </c>
+      <c r="D206">
+        <v>89</v>
+      </c>
+      <c r="E206">
+        <v>39</v>
+      </c>
+      <c r="F206">
+        <v>127</v>
+      </c>
+      <c r="G206">
+        <v>264</v>
+      </c>
+      <c r="H206">
+        <v>1616.5</v>
+      </c>
+      <c r="I206">
+        <v>1352.5</v>
+      </c>
+      <c r="J206" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10">
+      <c r="A207">
+        <v>1610</v>
+      </c>
+      <c r="B207">
+        <v>9516295</v>
+      </c>
+      <c r="C207">
+        <v>200</v>
+      </c>
+      <c r="D207">
+        <v>187</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+      <c r="F207">
+        <v>187</v>
+      </c>
+      <c r="G207">
+        <v>465</v>
+      </c>
+      <c r="H207">
+        <v>-200</v>
+      </c>
+      <c r="I207">
+        <v>-665</v>
+      </c>
+      <c r="J207" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10">
+      <c r="A208">
+        <v>1598</v>
+      </c>
+      <c r="B208">
+        <v>9493649</v>
+      </c>
+      <c r="C208">
+        <v>185</v>
+      </c>
+      <c r="D208">
+        <v>174</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208">
+        <v>174</v>
+      </c>
+      <c r="G208">
+        <v>432.5</v>
+      </c>
+      <c r="H208">
+        <v>-200</v>
+      </c>
+      <c r="I208">
+        <v>-632.5</v>
+      </c>
+      <c r="J208" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="A209">
+        <v>1856</v>
+      </c>
+      <c r="B209">
+        <v>9941989</v>
+      </c>
+      <c r="C209">
+        <v>172</v>
+      </c>
+      <c r="D209">
+        <v>123</v>
+      </c>
+      <c r="E209">
+        <v>36</v>
+      </c>
+      <c r="F209">
+        <v>158</v>
+      </c>
+      <c r="G209">
+        <v>366</v>
+      </c>
+      <c r="H209">
+        <v>1578</v>
+      </c>
+      <c r="I209">
+        <v>1212</v>
+      </c>
+      <c r="J209" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="A210">
+        <v>317</v>
+      </c>
+      <c r="B210">
+        <v>5824236</v>
+      </c>
+      <c r="C210">
+        <v>166</v>
+      </c>
+      <c r="D210">
+        <v>123</v>
+      </c>
+      <c r="E210">
+        <v>30</v>
+      </c>
+      <c r="F210">
+        <v>152</v>
+      </c>
+      <c r="G210">
+        <v>366</v>
+      </c>
+      <c r="H210">
+        <v>934.5</v>
+      </c>
+      <c r="I210">
+        <v>568.5</v>
+      </c>
+      <c r="J210" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
+      <c r="A211">
+        <v>661</v>
+      </c>
+      <c r="B211">
+        <v>5983968</v>
+      </c>
+      <c r="C211">
+        <v>160</v>
+      </c>
+      <c r="D211">
+        <v>134</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211">
+        <v>151</v>
+      </c>
+      <c r="G211">
+        <v>399</v>
+      </c>
+      <c r="H211">
+        <v>715.3</v>
+      </c>
+      <c r="I211">
+        <v>316.3</v>
+      </c>
+      <c r="J211" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="A212">
+        <v>301</v>
+      </c>
+      <c r="B212">
+        <v>5835682</v>
+      </c>
+      <c r="C212">
+        <v>202</v>
+      </c>
+      <c r="D212">
+        <v>191</v>
+      </c>
+      <c r="E212">
+        <v>1</v>
+      </c>
+      <c r="F212">
+        <v>191</v>
+      </c>
+      <c r="G212">
+        <v>475</v>
+      </c>
+      <c r="H212">
+        <v>-192.5</v>
+      </c>
+      <c r="I212">
+        <v>-667.5</v>
+      </c>
+      <c r="J212" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="A213">
+        <v>924</v>
+      </c>
+      <c r="B213">
+        <v>8349946</v>
+      </c>
+      <c r="C213">
+        <v>166</v>
+      </c>
+      <c r="D213">
+        <v>126</v>
+      </c>
+      <c r="E213">
+        <v>87</v>
+      </c>
+      <c r="F213">
+        <v>212</v>
+      </c>
+      <c r="G213">
+        <v>375</v>
+      </c>
+      <c r="H213">
+        <v>606.5</v>
+      </c>
+      <c r="I213">
+        <v>231.5</v>
+      </c>
+      <c r="J213" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="A214">
+        <v>1733</v>
+      </c>
+      <c r="B214">
+        <v>9732595</v>
+      </c>
+      <c r="C214">
+        <v>215</v>
+      </c>
+      <c r="D214">
+        <v>202</v>
+      </c>
+      <c r="E214">
+        <v>1</v>
+      </c>
+      <c r="F214">
+        <v>202</v>
+      </c>
+      <c r="G214">
+        <v>502.5</v>
+      </c>
+      <c r="H214">
+        <v>-62.452</v>
+      </c>
+      <c r="I214">
+        <v>-564.953</v>
+      </c>
+      <c r="J214" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
+      <c r="A215">
+        <v>387</v>
+      </c>
+      <c r="B215">
+        <v>4929736</v>
+      </c>
+      <c r="C215">
+        <v>250</v>
+      </c>
+      <c r="D215">
+        <v>196</v>
+      </c>
+      <c r="E215">
+        <v>35</v>
+      </c>
+      <c r="F215">
+        <v>230</v>
+      </c>
+      <c r="G215">
+        <v>390</v>
+      </c>
+      <c r="H215">
+        <v>1505</v>
+      </c>
+      <c r="I215">
+        <v>1115</v>
+      </c>
+      <c r="J215" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="A216">
+        <v>808</v>
+      </c>
+      <c r="B216">
+        <v>1791719</v>
+      </c>
+      <c r="C216">
+        <v>147</v>
+      </c>
+      <c r="D216">
+        <v>129</v>
+      </c>
+      <c r="E216">
+        <v>18</v>
+      </c>
+      <c r="F216">
+        <v>146</v>
+      </c>
+      <c r="G216">
+        <v>384</v>
+      </c>
+      <c r="H216">
+        <v>902.73</v>
+      </c>
+      <c r="I216">
+        <v>518.73</v>
+      </c>
+      <c r="J216" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="A217">
+        <v>69</v>
+      </c>
+      <c r="B217">
+        <v>5343075</v>
+      </c>
+      <c r="C217">
+        <v>168</v>
+      </c>
+      <c r="D217">
+        <v>126</v>
+      </c>
+      <c r="E217">
+        <v>28</v>
+      </c>
+      <c r="F217">
+        <v>153</v>
+      </c>
+      <c r="G217">
+        <v>375</v>
+      </c>
+      <c r="H217">
+        <v>-281.5</v>
+      </c>
+      <c r="I217">
+        <v>-656.5</v>
+      </c>
+      <c r="J217" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10">
+      <c r="A218">
+        <v>1591</v>
+      </c>
+      <c r="B218">
+        <v>9486038</v>
+      </c>
+      <c r="C218">
+        <v>201</v>
+      </c>
+      <c r="D218">
+        <v>193</v>
+      </c>
+      <c r="E218">
+        <v>1</v>
+      </c>
+      <c r="F218">
+        <v>193</v>
+      </c>
+      <c r="G218">
+        <v>480</v>
+      </c>
+      <c r="H218">
+        <v>-182.5</v>
+      </c>
+      <c r="I218">
+        <v>-662.5</v>
+      </c>
+      <c r="J218" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="A219">
+        <v>2023</v>
+      </c>
+      <c r="B219">
+        <v>6738589</v>
+      </c>
+      <c r="C219">
+        <v>217</v>
+      </c>
+      <c r="D219">
+        <v>208</v>
+      </c>
+      <c r="E219">
+        <v>1</v>
+      </c>
+      <c r="F219">
+        <v>208</v>
+      </c>
+      <c r="G219">
+        <v>517.5</v>
+      </c>
+      <c r="H219">
+        <v>-188.557</v>
+      </c>
+      <c r="I219">
+        <v>-706.057</v>
+      </c>
+      <c r="J219" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10">
+      <c r="A220">
+        <v>2032</v>
+      </c>
+      <c r="B220">
+        <v>6739045</v>
+      </c>
+      <c r="C220">
+        <v>202</v>
+      </c>
+      <c r="D220">
+        <v>186</v>
+      </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
+      <c r="F220">
+        <v>186</v>
+      </c>
+      <c r="G220">
+        <v>462.5</v>
+      </c>
+      <c r="H220">
+        <v>-382.147</v>
+      </c>
+      <c r="I220">
+        <v>-844.647</v>
+      </c>
+      <c r="J220" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
+      <c r="A221">
+        <v>2010</v>
+      </c>
+      <c r="B221">
+        <v>8418711</v>
+      </c>
+      <c r="C221">
+        <v>216</v>
+      </c>
+      <c r="D221">
+        <v>185</v>
+      </c>
+      <c r="E221">
+        <v>1</v>
+      </c>
+      <c r="F221">
+        <v>185</v>
+      </c>
+      <c r="G221">
+        <v>460</v>
+      </c>
+      <c r="H221">
+        <v>-186.342</v>
+      </c>
+      <c r="I221">
+        <v>-646.341</v>
+      </c>
+      <c r="J221" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="A222">
+        <v>46</v>
+      </c>
+      <c r="B222">
+        <v>5842402</v>
+      </c>
+      <c r="C222">
+        <v>151</v>
+      </c>
+      <c r="D222">
+        <v>131</v>
+      </c>
+      <c r="E222">
+        <v>21</v>
+      </c>
+      <c r="F222">
+        <v>151</v>
+      </c>
+      <c r="G222">
+        <v>390</v>
+      </c>
+      <c r="H222">
+        <v>-202.12</v>
+      </c>
+      <c r="I222">
+        <v>-592.12</v>
+      </c>
+      <c r="J222" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="A223">
+        <v>1436</v>
+      </c>
+      <c r="B223">
+        <v>9005877</v>
+      </c>
+      <c r="C223">
+        <v>162</v>
+      </c>
+      <c r="D223">
+        <v>126</v>
+      </c>
+      <c r="E223">
+        <v>36</v>
+      </c>
+      <c r="F223">
+        <v>161</v>
+      </c>
+      <c r="G223">
+        <v>375</v>
+      </c>
+      <c r="H223">
+        <v>799.97</v>
+      </c>
+      <c r="I223">
+        <v>424.97</v>
+      </c>
+      <c r="J223" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="A224">
+        <v>824</v>
+      </c>
+      <c r="B224">
+        <v>6262717</v>
+      </c>
+      <c r="C224">
+        <v>176</v>
+      </c>
+      <c r="D224">
+        <v>124</v>
+      </c>
+      <c r="E224">
+        <v>36</v>
+      </c>
+      <c r="F224">
+        <v>159</v>
+      </c>
+      <c r="G224">
+        <v>369</v>
+      </c>
+      <c r="H224">
+        <v>696.5</v>
+      </c>
+      <c r="I224">
+        <v>327.5</v>
+      </c>
+      <c r="J224" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10">
+      <c r="A225">
+        <v>895</v>
+      </c>
+      <c r="B225">
+        <v>8812147</v>
+      </c>
+      <c r="C225">
+        <v>184</v>
+      </c>
+      <c r="D225">
+        <v>183</v>
+      </c>
+      <c r="E225">
+        <v>1</v>
+      </c>
+      <c r="F225">
+        <v>183</v>
+      </c>
+      <c r="G225">
+        <v>455</v>
+      </c>
+      <c r="H225">
+        <v>-170</v>
+      </c>
+      <c r="I225">
+        <v>-625</v>
+      </c>
+      <c r="J225" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10">
+      <c r="A226">
+        <v>646</v>
+      </c>
+      <c r="B226">
+        <v>6010461</v>
+      </c>
+      <c r="C226">
+        <v>202</v>
+      </c>
+      <c r="D226">
+        <v>180</v>
+      </c>
+      <c r="E226">
+        <v>1</v>
+      </c>
+      <c r="F226">
+        <v>180</v>
+      </c>
+      <c r="G226">
+        <v>447.5</v>
+      </c>
+      <c r="H226">
+        <v>-172.367</v>
+      </c>
+      <c r="I226">
+        <v>-619.867</v>
+      </c>
+      <c r="J226" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10">
+      <c r="A227">
+        <v>354</v>
+      </c>
+      <c r="B227">
+        <v>430440</v>
+      </c>
+      <c r="C227">
+        <v>172</v>
+      </c>
+      <c r="D227">
+        <v>129</v>
+      </c>
+      <c r="E227">
+        <v>32</v>
+      </c>
+      <c r="F227">
+        <v>160</v>
+      </c>
+      <c r="G227">
+        <v>384</v>
+      </c>
+      <c r="H227">
+        <v>1496.5</v>
+      </c>
+      <c r="I227">
+        <v>1112.5</v>
+      </c>
+      <c r="J227" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10">
+      <c r="A228">
+        <v>1473</v>
+      </c>
+      <c r="B228">
+        <v>6743222</v>
+      </c>
+      <c r="C228">
+        <v>160</v>
+      </c>
+      <c r="D228">
+        <v>124</v>
+      </c>
+      <c r="E228">
+        <v>36</v>
+      </c>
+      <c r="F228">
+        <v>159</v>
+      </c>
+      <c r="G228">
+        <v>369</v>
+      </c>
+      <c r="H228">
+        <v>908</v>
+      </c>
+      <c r="I228">
+        <v>539</v>
+      </c>
+      <c r="J228" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10">
+      <c r="A229">
+        <v>1631</v>
+      </c>
+      <c r="B229">
+        <v>9549908</v>
+      </c>
+      <c r="C229">
+        <v>181</v>
+      </c>
+      <c r="D229">
+        <v>124</v>
+      </c>
+      <c r="E229">
+        <v>39</v>
+      </c>
+      <c r="F229">
+        <v>162</v>
+      </c>
+      <c r="G229">
+        <v>369</v>
+      </c>
+      <c r="H229">
+        <v>896.5</v>
+      </c>
+      <c r="I229">
+        <v>527.5</v>
+      </c>
+      <c r="J229" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10">
+      <c r="A230">
+        <v>466</v>
+      </c>
+      <c r="B230">
+        <v>1364871</v>
+      </c>
+      <c r="C230">
+        <v>185</v>
+      </c>
+      <c r="D230">
+        <v>170</v>
+      </c>
+      <c r="E230">
+        <v>1</v>
+      </c>
+      <c r="F230">
+        <v>170</v>
+      </c>
+      <c r="G230">
+        <v>422.5</v>
+      </c>
+      <c r="H230">
+        <v>-208.324</v>
+      </c>
+      <c r="I230">
+        <v>-630.824</v>
+      </c>
+      <c r="J230" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10">
+      <c r="A231">
+        <v>1200</v>
+      </c>
+      <c r="B231">
+        <v>8457993</v>
+      </c>
+      <c r="C231">
+        <v>185</v>
+      </c>
+      <c r="D231">
+        <v>181</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+      <c r="F231">
+        <v>181</v>
+      </c>
+      <c r="G231">
+        <v>450</v>
+      </c>
+      <c r="H231">
+        <v>-170</v>
+      </c>
+      <c r="I231">
+        <v>-620</v>
+      </c>
+      <c r="J231" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10">
+      <c r="A232">
+        <v>28</v>
+      </c>
+      <c r="B232">
+        <v>5949111</v>
+      </c>
+      <c r="C232">
+        <v>160</v>
+      </c>
+      <c r="D232">
+        <v>128</v>
+      </c>
+      <c r="E232">
+        <v>18</v>
+      </c>
+      <c r="F232">
+        <v>145</v>
+      </c>
+      <c r="G232">
+        <v>381</v>
+      </c>
+      <c r="H232">
+        <v>352.5</v>
+      </c>
+      <c r="I232">
+        <v>-28.5</v>
+      </c>
+      <c r="J232" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10">
+      <c r="A233">
+        <v>833</v>
+      </c>
+      <c r="B233">
+        <v>6741524</v>
+      </c>
+      <c r="C233">
+        <v>203</v>
+      </c>
+      <c r="D233">
+        <v>185</v>
+      </c>
+      <c r="E233">
+        <v>1</v>
+      </c>
+      <c r="F233">
+        <v>185</v>
+      </c>
+      <c r="G233">
+        <v>460</v>
+      </c>
+      <c r="H233">
+        <v>-142.5</v>
+      </c>
+      <c r="I233">
+        <v>-602.5</v>
+      </c>
+      <c r="J233" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10">
+      <c r="A234">
+        <v>1182</v>
+      </c>
+      <c r="B234">
+        <v>5024399</v>
+      </c>
+      <c r="C234">
+        <v>160</v>
+      </c>
+      <c r="D234">
+        <v>125</v>
+      </c>
+      <c r="E234">
+        <v>92</v>
+      </c>
+      <c r="F234">
+        <v>216</v>
+      </c>
+      <c r="G234">
+        <v>372</v>
+      </c>
+      <c r="H234">
+        <v>1427</v>
+      </c>
+      <c r="I234">
+        <v>1055</v>
+      </c>
+      <c r="J234" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10">
+      <c r="A235">
+        <v>1786</v>
+      </c>
+      <c r="B235">
+        <v>9814061</v>
+      </c>
+      <c r="C235">
+        <v>153</v>
+      </c>
+      <c r="D235">
+        <v>122</v>
+      </c>
+      <c r="E235">
+        <v>23</v>
+      </c>
+      <c r="F235">
+        <v>144</v>
+      </c>
+      <c r="G235">
+        <v>363</v>
+      </c>
+      <c r="H235">
+        <v>989</v>
+      </c>
+      <c r="I235">
+        <v>626</v>
+      </c>
+      <c r="J235" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10">
+      <c r="A236">
+        <v>1230</v>
+      </c>
+      <c r="B236">
+        <v>6738036</v>
+      </c>
+      <c r="C236">
+        <v>196</v>
+      </c>
+      <c r="D236">
+        <v>177</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+      <c r="F236">
+        <v>177</v>
+      </c>
+      <c r="G236">
+        <v>440</v>
+      </c>
+      <c r="H236">
+        <v>-197.5</v>
+      </c>
+      <c r="I236">
+        <v>-637.5</v>
+      </c>
+      <c r="J236" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10">
+      <c r="A237">
+        <v>795</v>
+      </c>
+      <c r="B237">
+        <v>8824341</v>
+      </c>
+      <c r="C237">
+        <v>160</v>
+      </c>
+      <c r="D237">
+        <v>126</v>
+      </c>
+      <c r="E237">
+        <v>79</v>
+      </c>
+      <c r="F237">
+        <v>204</v>
+      </c>
+      <c r="G237">
+        <v>375</v>
+      </c>
+      <c r="H237">
+        <v>1588.5</v>
+      </c>
+      <c r="I237">
+        <v>1213.5</v>
+      </c>
+      <c r="J237" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10">
+      <c r="A238">
+        <v>588</v>
+      </c>
+      <c r="B238">
+        <v>2814927</v>
+      </c>
+      <c r="C238">
+        <v>188</v>
+      </c>
+      <c r="D238">
+        <v>126</v>
+      </c>
+      <c r="E238">
+        <v>51</v>
+      </c>
+      <c r="F238">
+        <v>176</v>
+      </c>
+      <c r="G238">
+        <v>375</v>
+      </c>
+      <c r="H238">
+        <v>985.9</v>
+      </c>
+      <c r="I238">
+        <v>610.9</v>
+      </c>
+      <c r="J238" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10">
+      <c r="A239">
+        <v>1836</v>
+      </c>
+      <c r="B239">
+        <v>9887347</v>
+      </c>
+      <c r="C239">
+        <v>202</v>
+      </c>
+      <c r="D239">
+        <v>149</v>
+      </c>
+      <c r="E239">
+        <v>36</v>
+      </c>
+      <c r="F239">
+        <v>184</v>
+      </c>
+      <c r="G239">
+        <v>370</v>
+      </c>
+      <c r="H239">
+        <v>-261.341</v>
+      </c>
+      <c r="I239">
+        <v>-631.341</v>
+      </c>
+      <c r="J239" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10">
+      <c r="A240">
+        <v>327</v>
+      </c>
+      <c r="B240">
+        <v>5826150</v>
+      </c>
+      <c r="C240">
+        <v>155</v>
+      </c>
+      <c r="D240">
+        <v>125</v>
+      </c>
+      <c r="E240">
+        <v>28</v>
+      </c>
+      <c r="F240">
+        <v>152</v>
+      </c>
+      <c r="G240">
+        <v>372</v>
+      </c>
+      <c r="H240">
+        <v>1149.12</v>
+      </c>
+      <c r="I240">
+        <v>777.12</v>
+      </c>
+      <c r="J240" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10">
+      <c r="A241">
+        <v>1020</v>
+      </c>
+      <c r="B241">
+        <v>8408564</v>
+      </c>
+      <c r="C241">
+        <v>175</v>
+      </c>
+      <c r="D241">
+        <v>130</v>
+      </c>
+      <c r="E241">
+        <v>37</v>
+      </c>
+      <c r="F241">
+        <v>166</v>
+      </c>
+      <c r="G241">
+        <v>387</v>
+      </c>
+      <c r="H241">
+        <v>-431.5</v>
+      </c>
+      <c r="I241">
+        <v>-818.5</v>
+      </c>
+      <c r="J241" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10">
+      <c r="A242">
+        <v>1284</v>
+      </c>
+      <c r="B242">
+        <v>8753655</v>
+      </c>
+      <c r="C242">
+        <v>203</v>
+      </c>
+      <c r="D242">
+        <v>192</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+      <c r="F242">
+        <v>192</v>
+      </c>
+      <c r="G242">
+        <v>477.5</v>
+      </c>
+      <c r="H242">
+        <v>-209.52</v>
+      </c>
+      <c r="I242">
+        <v>-687.02</v>
+      </c>
+      <c r="J242" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10">
+      <c r="A243">
+        <v>1383</v>
+      </c>
+      <c r="B243">
+        <v>4350566</v>
+      </c>
+      <c r="C243">
+        <v>172</v>
+      </c>
+      <c r="D243">
+        <v>128</v>
+      </c>
+      <c r="E243">
+        <v>24</v>
+      </c>
+      <c r="F243">
+        <v>151</v>
+      </c>
+      <c r="G243">
+        <v>381</v>
+      </c>
+      <c r="H243">
+        <v>192</v>
+      </c>
+      <c r="I243">
+        <v>-189</v>
+      </c>
+      <c r="J243" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10">
+      <c r="A244">
+        <v>849</v>
+      </c>
+      <c r="B244">
+        <v>1356838</v>
+      </c>
+      <c r="C244">
+        <v>203</v>
+      </c>
+      <c r="D244">
+        <v>195</v>
+      </c>
+      <c r="E244">
+        <v>1</v>
+      </c>
+      <c r="F244">
+        <v>195</v>
+      </c>
+      <c r="G244">
+        <v>485</v>
+      </c>
+      <c r="H244">
+        <v>-185</v>
+      </c>
+      <c r="I244">
+        <v>-670</v>
+      </c>
+      <c r="J244" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10">
+      <c r="A245">
+        <v>1517</v>
+      </c>
+      <c r="B245">
+        <v>9002712</v>
+      </c>
+      <c r="C245">
+        <v>143</v>
+      </c>
+      <c r="D245">
+        <v>118</v>
+      </c>
+      <c r="E245">
+        <v>81</v>
+      </c>
+      <c r="F245">
+        <v>198</v>
+      </c>
+      <c r="G245">
+        <v>351</v>
+      </c>
+      <c r="H245">
+        <v>760.5</v>
+      </c>
+      <c r="I245">
+        <v>409.5</v>
+      </c>
+      <c r="J245" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10">
+      <c r="A246">
+        <v>285</v>
+      </c>
+      <c r="B246">
+        <v>5664059</v>
+      </c>
+      <c r="C246">
+        <v>183</v>
+      </c>
+      <c r="D246">
+        <v>181</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+      <c r="F246">
+        <v>181</v>
+      </c>
+      <c r="G246">
+        <v>450</v>
+      </c>
+      <c r="H246">
+        <v>-194.238</v>
+      </c>
+      <c r="I246">
+        <v>-644.2380000000001</v>
+      </c>
+      <c r="J246" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10">
+      <c r="A247">
+        <v>235</v>
+      </c>
+      <c r="B247">
+        <v>5586991</v>
+      </c>
+      <c r="C247">
+        <v>157</v>
+      </c>
+      <c r="D247">
+        <v>113</v>
+      </c>
+      <c r="E247">
+        <v>85</v>
+      </c>
+      <c r="F247">
+        <v>197</v>
+      </c>
+      <c r="G247">
+        <v>336</v>
+      </c>
+      <c r="H247">
+        <v>1539</v>
+      </c>
+      <c r="I247">
+        <v>1203</v>
+      </c>
+      <c r="J247" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10">
+      <c r="A248">
+        <v>709</v>
+      </c>
+      <c r="B248">
+        <v>3242550</v>
+      </c>
+      <c r="C248">
+        <v>156</v>
+      </c>
+      <c r="D248">
+        <v>133</v>
+      </c>
+      <c r="E248">
+        <v>23</v>
+      </c>
+      <c r="F248">
+        <v>155</v>
+      </c>
+      <c r="G248">
+        <v>396</v>
+      </c>
+      <c r="H248">
+        <v>826.1799999999999</v>
+      </c>
+      <c r="I248">
+        <v>430.18</v>
+      </c>
+      <c r="J248" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10">
+      <c r="A249">
+        <v>256</v>
+      </c>
+      <c r="B249">
+        <v>5580240</v>
+      </c>
+      <c r="C249">
+        <v>155</v>
+      </c>
+      <c r="D249">
+        <v>125</v>
+      </c>
+      <c r="E249">
+        <v>96</v>
+      </c>
+      <c r="F249">
+        <v>220</v>
+      </c>
+      <c r="G249">
+        <v>372</v>
+      </c>
+      <c r="H249">
+        <v>825</v>
+      </c>
+      <c r="I249">
+        <v>453</v>
+      </c>
+      <c r="J249" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10">
+      <c r="A250">
+        <v>1272</v>
+      </c>
+      <c r="B250">
+        <v>8824666</v>
+      </c>
+      <c r="C250">
+        <v>134</v>
+      </c>
+      <c r="D250">
+        <v>123</v>
+      </c>
+      <c r="E250">
+        <v>11</v>
+      </c>
+      <c r="F250">
+        <v>133</v>
+      </c>
+      <c r="G250">
+        <v>366</v>
+      </c>
+      <c r="H250">
+        <v>887.61</v>
+      </c>
+      <c r="I250">
+        <v>521.61</v>
+      </c>
+      <c r="J250" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10">
+      <c r="A251">
+        <v>1583</v>
+      </c>
+      <c r="B251">
+        <v>9466763</v>
+      </c>
+      <c r="C251">
+        <v>190</v>
+      </c>
+      <c r="D251">
+        <v>180</v>
+      </c>
+      <c r="E251">
+        <v>1</v>
+      </c>
+      <c r="F251">
+        <v>180</v>
+      </c>
+      <c r="G251">
+        <v>447.5</v>
+      </c>
+      <c r="H251">
+        <v>-205</v>
+      </c>
+      <c r="I251">
+        <v>-652.5</v>
+      </c>
+      <c r="J251" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10">
+      <c r="A252">
+        <v>1866</v>
+      </c>
+      <c r="B252">
+        <v>9963566</v>
+      </c>
+      <c r="C252">
+        <v>182</v>
+      </c>
+      <c r="D252">
+        <v>132</v>
+      </c>
+      <c r="E252">
+        <v>48</v>
+      </c>
+      <c r="F252">
+        <v>179</v>
+      </c>
+      <c r="G252">
+        <v>393</v>
+      </c>
+      <c r="H252">
+        <v>309.5</v>
+      </c>
+      <c r="I252">
+        <v>-83.5</v>
+      </c>
+      <c r="J252" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10">
+      <c r="A253">
+        <v>1954</v>
+      </c>
+      <c r="B253">
+        <v>1016097</v>
+      </c>
+      <c r="C253">
+        <v>149</v>
+      </c>
+      <c r="D253">
+        <v>112</v>
+      </c>
+      <c r="E253">
+        <v>27</v>
+      </c>
+      <c r="F253">
+        <v>138</v>
+      </c>
+      <c r="G253">
+        <v>333</v>
+      </c>
+      <c r="H253">
+        <v>-203.4</v>
+      </c>
+      <c r="I253">
+        <v>-536.4</v>
+      </c>
+      <c r="J253" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10">
+      <c r="A254">
+        <v>1081</v>
+      </c>
+      <c r="B254">
+        <v>8472684</v>
+      </c>
+      <c r="C254">
+        <v>161</v>
+      </c>
+      <c r="D254">
+        <v>121</v>
+      </c>
+      <c r="E254">
+        <v>88</v>
+      </c>
+      <c r="F254">
+        <v>208</v>
+      </c>
+      <c r="G254">
+        <v>360</v>
+      </c>
+      <c r="H254">
+        <v>1542</v>
+      </c>
+      <c r="I254">
+        <v>1182</v>
+      </c>
+      <c r="J254" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10">
+      <c r="A255">
+        <v>77</v>
+      </c>
+      <c r="B255">
+        <v>5028171</v>
+      </c>
+      <c r="C255">
+        <v>158</v>
+      </c>
+      <c r="D255">
+        <v>122</v>
+      </c>
+      <c r="E255">
+        <v>94</v>
+      </c>
+      <c r="F255">
+        <v>215</v>
+      </c>
+      <c r="G255">
+        <v>363</v>
+      </c>
+      <c r="H255">
+        <v>-534</v>
+      </c>
+      <c r="I255">
+        <v>-897</v>
+      </c>
+      <c r="J255" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10">
+      <c r="A256">
+        <v>468</v>
+      </c>
+      <c r="B256">
+        <v>1199519</v>
+      </c>
+      <c r="C256">
+        <v>143</v>
+      </c>
+      <c r="D256">
+        <v>126</v>
+      </c>
+      <c r="E256">
+        <v>16</v>
+      </c>
+      <c r="F256">
+        <v>141</v>
+      </c>
+      <c r="G256">
+        <v>375</v>
+      </c>
+      <c r="H256">
+        <v>844.88</v>
+      </c>
+      <c r="I256">
+        <v>469.88</v>
+      </c>
+      <c r="J256" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
+      <c r="A257">
+        <v>473</v>
+      </c>
+      <c r="B257">
+        <v>4787996</v>
+      </c>
+      <c r="C257">
+        <v>119</v>
+      </c>
+      <c r="D257">
+        <v>110</v>
+      </c>
+      <c r="E257">
+        <v>10</v>
+      </c>
+      <c r="F257">
+        <v>119</v>
+      </c>
+      <c r="G257">
+        <v>327</v>
+      </c>
+      <c r="H257">
+        <v>828.33</v>
+      </c>
+      <c r="I257">
+        <v>501.33</v>
+      </c>
+      <c r="J257" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10">
+      <c r="A258">
+        <v>644</v>
+      </c>
+      <c r="B258">
+        <v>6013820</v>
+      </c>
+      <c r="C258">
+        <v>166</v>
+      </c>
+      <c r="D258">
+        <v>119</v>
+      </c>
+      <c r="E258">
+        <v>34</v>
+      </c>
+      <c r="F258">
+        <v>152</v>
+      </c>
+      <c r="G258">
+        <v>354</v>
+      </c>
+      <c r="H258">
+        <v>1254</v>
+      </c>
+      <c r="I258">
+        <v>900</v>
+      </c>
+      <c r="J258" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10">
+      <c r="A259">
+        <v>55</v>
+      </c>
+      <c r="B259">
+        <v>5484235</v>
+      </c>
+      <c r="C259">
+        <v>153</v>
+      </c>
+      <c r="D259">
+        <v>122</v>
+      </c>
+      <c r="E259">
+        <v>32</v>
+      </c>
+      <c r="F259">
+        <v>153</v>
+      </c>
+      <c r="G259">
+        <v>363</v>
+      </c>
+      <c r="H259">
+        <v>774.72</v>
+      </c>
+      <c r="I259">
+        <v>411.72</v>
+      </c>
+      <c r="J259" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10">
+      <c r="A260">
+        <v>165</v>
+      </c>
+      <c r="B260">
+        <v>5676496</v>
+      </c>
+      <c r="C260">
+        <v>194</v>
+      </c>
+      <c r="D260">
+        <v>133</v>
+      </c>
+      <c r="E260">
+        <v>36</v>
+      </c>
+      <c r="F260">
+        <v>168</v>
+      </c>
+      <c r="G260">
+        <v>330</v>
+      </c>
+      <c r="H260">
+        <v>-265.055</v>
+      </c>
+      <c r="I260">
+        <v>-595.0549999999999</v>
+      </c>
+      <c r="J260" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10">
+      <c r="A261">
+        <v>1300</v>
+      </c>
+      <c r="B261">
+        <v>8675301</v>
+      </c>
+      <c r="C261">
+        <v>226</v>
+      </c>
+      <c r="D261">
+        <v>129</v>
+      </c>
+      <c r="E261">
+        <v>84</v>
+      </c>
+      <c r="F261">
+        <v>212</v>
+      </c>
+      <c r="G261">
+        <v>384</v>
+      </c>
+      <c r="H261">
+        <v>-245.5</v>
+      </c>
+      <c r="I261">
+        <v>-629.5</v>
+      </c>
+      <c r="J261" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
+      <c r="A262">
+        <v>1518</v>
+      </c>
+      <c r="B262">
+        <v>9005615</v>
+      </c>
+      <c r="C262">
+        <v>192</v>
+      </c>
+      <c r="D262">
+        <v>191</v>
+      </c>
+      <c r="E262">
+        <v>1</v>
+      </c>
+      <c r="F262">
+        <v>191</v>
+      </c>
+      <c r="G262">
+        <v>475</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>-475</v>
+      </c>
+      <c r="J262" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10">
+      <c r="A263">
+        <v>1869</v>
+      </c>
+      <c r="B263">
+        <v>9967296</v>
+      </c>
+      <c r="C263">
+        <v>177</v>
+      </c>
+      <c r="D263">
+        <v>121</v>
+      </c>
+      <c r="E263">
+        <v>41</v>
+      </c>
+      <c r="F263">
+        <v>161</v>
+      </c>
+      <c r="G263">
+        <v>360</v>
+      </c>
+      <c r="H263">
+        <v>558</v>
+      </c>
+      <c r="I263">
+        <v>198</v>
+      </c>
+      <c r="J263" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10">
+      <c r="A264">
+        <v>613</v>
+      </c>
+      <c r="B264">
+        <v>5027476</v>
+      </c>
+      <c r="C264">
+        <v>239</v>
+      </c>
+      <c r="D264">
+        <v>186</v>
+      </c>
+      <c r="E264">
+        <v>38</v>
+      </c>
+      <c r="F264">
+        <v>223</v>
+      </c>
+      <c r="G264">
+        <v>370</v>
+      </c>
+      <c r="H264">
+        <v>900.3</v>
+      </c>
+      <c r="I264">
+        <v>530.3</v>
+      </c>
+      <c r="J264" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10">
+      <c r="A265">
+        <v>338</v>
+      </c>
+      <c r="B265">
+        <v>5768375</v>
+      </c>
+      <c r="C265">
+        <v>177</v>
+      </c>
+      <c r="D265">
+        <v>133</v>
+      </c>
+      <c r="E265">
+        <v>92</v>
+      </c>
+      <c r="F265">
+        <v>224</v>
+      </c>
+      <c r="G265">
+        <v>396</v>
+      </c>
+      <c r="H265">
+        <v>-278.5</v>
+      </c>
+      <c r="I265">
+        <v>-674.5</v>
+      </c>
+      <c r="J265" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
+      <c r="A266">
+        <v>755</v>
+      </c>
+      <c r="B266">
+        <v>6110072</v>
+      </c>
+      <c r="C266">
+        <v>148</v>
+      </c>
+      <c r="D266">
+        <v>130</v>
+      </c>
+      <c r="E266">
+        <v>15</v>
+      </c>
+      <c r="F266">
+        <v>144</v>
+      </c>
+      <c r="G266">
+        <v>387</v>
+      </c>
+      <c r="H266">
+        <v>1050.5</v>
+      </c>
+      <c r="I266">
+        <v>663.5</v>
+      </c>
+      <c r="J266" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
+      <c r="A267">
+        <v>603</v>
+      </c>
+      <c r="B267">
+        <v>5660543</v>
+      </c>
+      <c r="C267">
+        <v>158</v>
+      </c>
+      <c r="D267">
+        <v>122</v>
+      </c>
+      <c r="E267">
+        <v>34</v>
+      </c>
+      <c r="F267">
+        <v>155</v>
+      </c>
+      <c r="G267">
+        <v>363</v>
+      </c>
+      <c r="H267">
+        <v>848.21</v>
+      </c>
+      <c r="I267">
+        <v>485.21</v>
+      </c>
+      <c r="J267" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10">
+      <c r="A268">
+        <v>1710</v>
+      </c>
+      <c r="B268">
+        <v>9683040</v>
+      </c>
+      <c r="C268">
+        <v>156</v>
+      </c>
+      <c r="D268">
+        <v>126</v>
+      </c>
+      <c r="E268">
+        <v>25</v>
+      </c>
+      <c r="F268">
+        <v>150</v>
+      </c>
+      <c r="G268">
+        <v>375</v>
+      </c>
+      <c r="H268">
+        <v>862.5</v>
+      </c>
+      <c r="I268">
+        <v>487.5</v>
+      </c>
+      <c r="J268" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10">
+      <c r="A269">
+        <v>1039</v>
+      </c>
+      <c r="B269">
+        <v>1711665</v>
+      </c>
+      <c r="C269">
+        <v>181</v>
+      </c>
+      <c r="D269">
+        <v>177</v>
+      </c>
+      <c r="E269">
+        <v>1</v>
+      </c>
+      <c r="F269">
+        <v>177</v>
+      </c>
+      <c r="G269">
+        <v>440</v>
+      </c>
+      <c r="H269">
+        <v>-167.5</v>
+      </c>
+      <c r="I269">
+        <v>-607.5</v>
+      </c>
+      <c r="J269" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10">
+      <c r="A270">
+        <v>1784</v>
+      </c>
+      <c r="B270">
+        <v>9812531</v>
+      </c>
+      <c r="C270">
+        <v>158</v>
+      </c>
+      <c r="D270">
+        <v>126</v>
+      </c>
+      <c r="E270">
+        <v>16</v>
+      </c>
+      <c r="F270">
+        <v>141</v>
+      </c>
+      <c r="G270">
+        <v>375</v>
+      </c>
+      <c r="H270">
+        <v>203.32</v>
+      </c>
+      <c r="I270">
+        <v>-171.68</v>
+      </c>
+      <c r="J270" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10">
+      <c r="A271">
+        <v>1661</v>
+      </c>
+      <c r="B271">
+        <v>9614974</v>
+      </c>
+      <c r="C271">
+        <v>166</v>
+      </c>
+      <c r="D271">
+        <v>125</v>
+      </c>
+      <c r="E271">
+        <v>87</v>
+      </c>
+      <c r="F271">
+        <v>211</v>
+      </c>
+      <c r="G271">
+        <v>372</v>
+      </c>
+      <c r="H271">
+        <v>897.5</v>
+      </c>
+      <c r="I271">
+        <v>525.5</v>
+      </c>
+      <c r="J271" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10">
+      <c r="A272">
+        <v>1483</v>
+      </c>
+      <c r="B272">
+        <v>9019431</v>
+      </c>
+      <c r="C272">
+        <v>174</v>
+      </c>
+      <c r="D272">
+        <v>130</v>
+      </c>
+      <c r="E272">
+        <v>25</v>
+      </c>
+      <c r="F272">
+        <v>154</v>
+      </c>
+      <c r="G272">
+        <v>387</v>
+      </c>
+      <c r="H272">
+        <v>819.5</v>
+      </c>
+      <c r="I272">
+        <v>432.5</v>
+      </c>
+      <c r="J272" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10">
+      <c r="A273">
+        <v>1310</v>
+      </c>
+      <c r="B273">
+        <v>8566270</v>
+      </c>
+      <c r="C273">
+        <v>160</v>
+      </c>
+      <c r="D273">
+        <v>136</v>
+      </c>
+      <c r="E273">
+        <v>91</v>
+      </c>
+      <c r="F273">
+        <v>226</v>
+      </c>
+      <c r="G273">
+        <v>405</v>
+      </c>
+      <c r="H273">
+        <v>-144.1</v>
+      </c>
+      <c r="I273">
+        <v>-549.1</v>
+      </c>
+      <c r="J273" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10">
+      <c r="A274">
+        <v>344</v>
+      </c>
+      <c r="B274">
+        <v>5903760</v>
+      </c>
+      <c r="C274">
+        <v>159</v>
+      </c>
+      <c r="D274">
+        <v>124</v>
+      </c>
+      <c r="E274">
+        <v>22</v>
+      </c>
+      <c r="F274">
+        <v>145</v>
+      </c>
+      <c r="G274">
+        <v>369</v>
+      </c>
+      <c r="H274">
+        <v>-361</v>
+      </c>
+      <c r="I274">
+        <v>-730</v>
+      </c>
+      <c r="J274" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10">
+      <c r="A275">
+        <v>1640</v>
+      </c>
+      <c r="B275">
+        <v>9577058</v>
+      </c>
+      <c r="C275">
+        <v>190</v>
+      </c>
+      <c r="D275">
+        <v>165</v>
+      </c>
+      <c r="E275">
+        <v>1</v>
+      </c>
+      <c r="F275">
+        <v>165</v>
+      </c>
+      <c r="G275">
+        <v>410</v>
+      </c>
+      <c r="H275">
+        <v>-187.5</v>
+      </c>
+      <c r="I275">
+        <v>-597.5</v>
+      </c>
+      <c r="J275" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10">
+      <c r="A276">
+        <v>1986</v>
+      </c>
+      <c r="B276">
+        <v>6046005</v>
+      </c>
+      <c r="C276">
+        <v>163</v>
+      </c>
+      <c r="D276">
+        <v>121</v>
+      </c>
+      <c r="E276">
+        <v>33</v>
+      </c>
+      <c r="F276">
+        <v>153</v>
+      </c>
+      <c r="G276">
+        <v>360</v>
+      </c>
+      <c r="H276">
+        <v>939</v>
+      </c>
+      <c r="I276">
+        <v>579</v>
+      </c>
+      <c r="J276" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10">
+      <c r="A277">
+        <v>44</v>
+      </c>
+      <c r="B277">
+        <v>5026272</v>
+      </c>
+      <c r="C277">
+        <v>247</v>
+      </c>
+      <c r="D277">
+        <v>187</v>
+      </c>
+      <c r="E277">
+        <v>32</v>
+      </c>
+      <c r="F277">
+        <v>218</v>
+      </c>
+      <c r="G277">
+        <v>372</v>
+      </c>
+      <c r="H277">
+        <v>869</v>
+      </c>
+      <c r="I277">
+        <v>497</v>
+      </c>
+      <c r="J277" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10">
+      <c r="A278">
+        <v>108</v>
+      </c>
+      <c r="B278">
+        <v>5452306</v>
+      </c>
+      <c r="C278">
+        <v>169</v>
+      </c>
+      <c r="D278">
+        <v>116</v>
+      </c>
+      <c r="E278">
+        <v>44</v>
+      </c>
+      <c r="F278">
+        <v>159</v>
+      </c>
+      <c r="G278">
+        <v>345</v>
+      </c>
+      <c r="H278">
+        <v>8.9</v>
+      </c>
+      <c r="I278">
+        <v>-336.1</v>
+      </c>
+      <c r="J278" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10">
+      <c r="A279">
+        <v>307</v>
+      </c>
+      <c r="B279">
+        <v>5730942</v>
+      </c>
+      <c r="C279">
+        <v>202</v>
+      </c>
+      <c r="D279">
+        <v>175</v>
+      </c>
+      <c r="E279">
+        <v>1</v>
+      </c>
+      <c r="F279">
+        <v>175</v>
+      </c>
+      <c r="G279">
+        <v>435</v>
+      </c>
+      <c r="H279">
+        <v>-200</v>
+      </c>
+      <c r="I279">
+        <v>-635</v>
+      </c>
+      <c r="J279" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10">
+      <c r="A280">
+        <v>872</v>
+      </c>
+      <c r="B280">
+        <v>8851572</v>
+      </c>
+      <c r="C280">
+        <v>149</v>
+      </c>
+      <c r="D280">
+        <v>124</v>
+      </c>
+      <c r="E280">
+        <v>25</v>
+      </c>
+      <c r="F280">
+        <v>148</v>
+      </c>
+      <c r="G280">
+        <v>369</v>
+      </c>
+      <c r="H280">
+        <v>391.34</v>
+      </c>
+      <c r="I280">
+        <v>22.34</v>
+      </c>
+      <c r="J280" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10">
+      <c r="A281">
+        <v>628</v>
+      </c>
+      <c r="B281">
+        <v>5023110</v>
+      </c>
+      <c r="C281">
+        <v>194</v>
+      </c>
+      <c r="D281">
+        <v>184</v>
+      </c>
+      <c r="E281">
+        <v>1</v>
+      </c>
+      <c r="F281">
+        <v>184</v>
+      </c>
+      <c r="G281">
+        <v>457.5</v>
+      </c>
+      <c r="H281">
+        <v>-137.5</v>
+      </c>
+      <c r="I281">
+        <v>-595</v>
+      </c>
+      <c r="J281" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10">
+      <c r="A282">
+        <v>1910</v>
+      </c>
+      <c r="B282">
+        <v>9745889</v>
+      </c>
+      <c r="C282">
+        <v>179</v>
+      </c>
+      <c r="D282">
+        <v>168</v>
+      </c>
+      <c r="E282">
+        <v>1</v>
+      </c>
+      <c r="F282">
+        <v>168</v>
+      </c>
+      <c r="G282">
+        <v>417.5</v>
+      </c>
+      <c r="H282">
+        <v>-198.389</v>
+      </c>
+      <c r="I282">
+        <v>-615.889</v>
+      </c>
+      <c r="J282" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10">
+      <c r="A283">
+        <v>161</v>
+      </c>
+      <c r="B283">
+        <v>5263493</v>
+      </c>
+      <c r="C283">
+        <v>147</v>
+      </c>
+      <c r="D283">
+        <v>127</v>
+      </c>
+      <c r="E283">
+        <v>20</v>
+      </c>
+      <c r="F283">
+        <v>146</v>
+      </c>
+      <c r="G283">
+        <v>378</v>
+      </c>
+      <c r="H283">
+        <v>1347.81</v>
+      </c>
+      <c r="I283">
+        <v>969.8099999999999</v>
+      </c>
+      <c r="J283" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10">
+      <c r="A284">
+        <v>426</v>
+      </c>
+      <c r="B284">
+        <v>671458</v>
+      </c>
+      <c r="C284">
+        <v>184</v>
+      </c>
+      <c r="D284">
+        <v>148</v>
+      </c>
+      <c r="E284">
+        <v>29</v>
+      </c>
+      <c r="F284">
+        <v>176</v>
+      </c>
+      <c r="G284">
+        <v>367.5</v>
+      </c>
+      <c r="H284">
+        <v>-298.77</v>
+      </c>
+      <c r="I284">
+        <v>-666.27</v>
+      </c>
+      <c r="J284" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10">
+      <c r="A285">
+        <v>1612</v>
+      </c>
+      <c r="B285">
+        <v>9518476</v>
+      </c>
+      <c r="C285">
+        <v>199</v>
+      </c>
+      <c r="D285">
+        <v>178</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
+      <c r="F285">
+        <v>178</v>
+      </c>
+      <c r="G285">
+        <v>442.5</v>
+      </c>
+      <c r="H285">
+        <v>-192.5</v>
+      </c>
+      <c r="I285">
+        <v>-635</v>
+      </c>
+      <c r="J285" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10">
+      <c r="A286">
+        <v>1493</v>
+      </c>
+      <c r="B286">
+        <v>9005823</v>
+      </c>
+      <c r="C286">
+        <v>150</v>
+      </c>
+      <c r="D286">
+        <v>114</v>
+      </c>
+      <c r="E286">
+        <v>29</v>
+      </c>
+      <c r="F286">
+        <v>142</v>
+      </c>
+      <c r="G286">
+        <v>339</v>
+      </c>
+      <c r="H286">
+        <v>-170</v>
+      </c>
+      <c r="I286">
+        <v>-509</v>
+      </c>
+      <c r="J286" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10">
+      <c r="A287">
+        <v>764</v>
+      </c>
+      <c r="B287">
+        <v>6136166</v>
+      </c>
+      <c r="C287">
+        <v>180</v>
+      </c>
+      <c r="D287">
+        <v>164</v>
+      </c>
+      <c r="E287">
+        <v>1</v>
+      </c>
+      <c r="F287">
+        <v>164</v>
+      </c>
+      <c r="G287">
+        <v>407.5</v>
+      </c>
+      <c r="H287">
+        <v>-177.5</v>
+      </c>
+      <c r="I287">
+        <v>-585</v>
+      </c>
+      <c r="J287" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10">
+      <c r="A288">
+        <v>160</v>
+      </c>
+      <c r="B288">
+        <v>5360460</v>
+      </c>
+      <c r="C288">
+        <v>131</v>
+      </c>
+      <c r="D288">
+        <v>111</v>
+      </c>
+      <c r="E288">
+        <v>21</v>
+      </c>
+      <c r="F288">
+        <v>131</v>
+      </c>
+      <c r="G288">
+        <v>329.99</v>
+      </c>
+      <c r="H288">
+        <v>857.64</v>
+      </c>
+      <c r="I288">
+        <v>527.65</v>
+      </c>
+      <c r="J288" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10">
+      <c r="A289">
+        <v>1089</v>
+      </c>
+      <c r="B289">
+        <v>8511452</v>
+      </c>
+      <c r="C289">
+        <v>189</v>
+      </c>
+      <c r="D289">
+        <v>183</v>
+      </c>
+      <c r="E289">
+        <v>1</v>
+      </c>
+      <c r="F289">
+        <v>183</v>
+      </c>
+      <c r="G289">
+        <v>455</v>
+      </c>
+      <c r="H289">
+        <v>-177.5</v>
+      </c>
+      <c r="I289">
+        <v>-632.5</v>
+      </c>
+      <c r="J289" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10">
+      <c r="A290">
+        <v>761</v>
+      </c>
+      <c r="B290">
+        <v>6130088</v>
+      </c>
+      <c r="C290">
+        <v>175</v>
+      </c>
+      <c r="D290">
+        <v>175</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290">
+        <v>175</v>
+      </c>
+      <c r="G290">
+        <v>435</v>
+      </c>
+      <c r="H290">
+        <v>-215</v>
+      </c>
+      <c r="I290">
+        <v>-650</v>
+      </c>
+      <c r="J290" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10">
+      <c r="A291">
+        <v>2060</v>
+      </c>
+      <c r="B291">
+        <v>10013411</v>
+      </c>
+      <c r="C291">
+        <v>198</v>
+      </c>
+      <c r="D291">
+        <v>155</v>
+      </c>
+      <c r="E291">
+        <v>25</v>
+      </c>
+      <c r="F291">
+        <v>179</v>
+      </c>
+      <c r="G291">
+        <v>385</v>
+      </c>
+      <c r="H291">
+        <v>-285.374</v>
+      </c>
+      <c r="I291">
+        <v>-670.374</v>
+      </c>
+      <c r="J291" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10">
+      <c r="A292">
+        <v>918</v>
+      </c>
+      <c r="B292">
+        <v>2458139</v>
+      </c>
+      <c r="C292">
+        <v>167</v>
+      </c>
+      <c r="D292">
+        <v>134</v>
+      </c>
+      <c r="E292">
+        <v>21</v>
+      </c>
+      <c r="F292">
+        <v>154</v>
+      </c>
+      <c r="G292">
+        <v>399</v>
+      </c>
+      <c r="H292">
+        <v>1098</v>
+      </c>
+      <c r="I292">
+        <v>699</v>
+      </c>
+      <c r="J292" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10">
+      <c r="A293">
+        <v>1399</v>
+      </c>
+      <c r="B293">
+        <v>9479088</v>
+      </c>
+      <c r="C293">
+        <v>162</v>
+      </c>
+      <c r="D293">
+        <v>128</v>
+      </c>
+      <c r="E293">
+        <v>22</v>
+      </c>
+      <c r="F293">
+        <v>149</v>
+      </c>
+      <c r="G293">
+        <v>381</v>
+      </c>
+      <c r="H293">
+        <v>1482</v>
+      </c>
+      <c r="I293">
+        <v>1101</v>
+      </c>
+      <c r="J293" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10">
+      <c r="A294">
+        <v>1874</v>
+      </c>
+      <c r="B294">
+        <v>9975123</v>
+      </c>
+      <c r="C294">
+        <v>169</v>
+      </c>
+      <c r="D294">
+        <v>124</v>
+      </c>
+      <c r="E294">
+        <v>29</v>
+      </c>
+      <c r="F294">
+        <v>152</v>
+      </c>
+      <c r="G294">
+        <v>369</v>
+      </c>
+      <c r="H294">
+        <v>470</v>
+      </c>
+      <c r="I294">
+        <v>101</v>
+      </c>
+      <c r="J294" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10">
+      <c r="A295">
+        <v>182</v>
+      </c>
+      <c r="B295">
+        <v>5660595</v>
+      </c>
+      <c r="C295">
+        <v>153</v>
+      </c>
+      <c r="D295">
+        <v>128</v>
+      </c>
+      <c r="E295">
+        <v>26</v>
+      </c>
+      <c r="F295">
+        <v>153</v>
+      </c>
+      <c r="G295">
+        <v>381</v>
+      </c>
+      <c r="H295">
+        <v>879.8099999999999</v>
+      </c>
+      <c r="I295">
+        <v>498.81</v>
+      </c>
+      <c r="J295" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10">
+      <c r="A296">
+        <v>441</v>
+      </c>
+      <c r="B296">
+        <v>3426570</v>
+      </c>
+      <c r="C296">
+        <v>179</v>
+      </c>
+      <c r="D296">
+        <v>128</v>
+      </c>
+      <c r="E296">
+        <v>29</v>
+      </c>
+      <c r="F296">
+        <v>156</v>
+      </c>
+      <c r="G296">
+        <v>381</v>
+      </c>
+      <c r="H296">
+        <v>-350.5</v>
+      </c>
+      <c r="I296">
+        <v>-731.5</v>
+      </c>
+      <c r="J296" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10">
+      <c r="A297">
+        <v>1035</v>
+      </c>
+      <c r="B297">
+        <v>6742059</v>
+      </c>
+      <c r="C297">
+        <v>131</v>
+      </c>
+      <c r="D297">
+        <v>114</v>
+      </c>
+      <c r="E297">
+        <v>18</v>
+      </c>
+      <c r="F297">
+        <v>131</v>
+      </c>
+      <c r="G297">
+        <v>339</v>
+      </c>
+      <c r="H297">
+        <v>987.22</v>
+      </c>
+      <c r="I297">
+        <v>648.22</v>
+      </c>
+      <c r="J297" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10">
+      <c r="A298">
+        <v>488</v>
+      </c>
+      <c r="B298">
+        <v>1449355</v>
+      </c>
+      <c r="C298">
+        <v>143</v>
+      </c>
+      <c r="D298">
+        <v>125</v>
+      </c>
+      <c r="E298">
+        <v>19</v>
+      </c>
+      <c r="F298">
+        <v>143</v>
+      </c>
+      <c r="G298">
+        <v>372</v>
+      </c>
+      <c r="H298">
+        <v>876.65</v>
+      </c>
+      <c r="I298">
+        <v>504.65</v>
+      </c>
+      <c r="J298" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10">
+      <c r="A299">
+        <v>154</v>
+      </c>
+      <c r="B299">
+        <v>5139514</v>
+      </c>
+      <c r="C299">
+        <v>257</v>
+      </c>
+      <c r="D299">
+        <v>180</v>
+      </c>
+      <c r="E299">
+        <v>47</v>
+      </c>
+      <c r="F299">
+        <v>226</v>
+      </c>
+      <c r="G299">
+        <v>358</v>
+      </c>
+      <c r="H299">
+        <v>-227.4</v>
+      </c>
+      <c r="I299">
+        <v>-585.4</v>
+      </c>
+      <c r="J299" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10">
+      <c r="A300">
+        <v>1777</v>
+      </c>
+      <c r="B300">
+        <v>9794940</v>
+      </c>
+      <c r="C300">
+        <v>184</v>
+      </c>
+      <c r="D300">
+        <v>175</v>
+      </c>
+      <c r="E300">
+        <v>1</v>
+      </c>
+      <c r="F300">
+        <v>175</v>
+      </c>
+      <c r="G300">
+        <v>435</v>
+      </c>
+      <c r="H300">
+        <v>-232.107</v>
+      </c>
+      <c r="I300">
+        <v>-667.107</v>
+      </c>
+      <c r="J300" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10">
+      <c r="A301">
+        <v>970</v>
+      </c>
+      <c r="B301">
+        <v>8489859</v>
+      </c>
+      <c r="C301">
+        <v>164</v>
+      </c>
+      <c r="D301">
+        <v>119</v>
+      </c>
+      <c r="E301">
+        <v>30</v>
+      </c>
+      <c r="F301">
+        <v>148</v>
+      </c>
+      <c r="G301">
+        <v>354</v>
+      </c>
+      <c r="H301">
+        <v>-487.5</v>
+      </c>
+      <c r="I301">
+        <v>-841.5</v>
+      </c>
+      <c r="J301" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10">
+      <c r="A302">
+        <v>1409</v>
+      </c>
+      <c r="B302">
+        <v>8479024</v>
+      </c>
+      <c r="C302">
+        <v>173</v>
+      </c>
+      <c r="D302">
+        <v>131</v>
+      </c>
+      <c r="E302">
+        <v>31</v>
+      </c>
+      <c r="F302">
+        <v>161</v>
+      </c>
+      <c r="G302">
+        <v>390</v>
+      </c>
+      <c r="H302">
+        <v>892.6</v>
+      </c>
+      <c r="I302">
+        <v>502.6</v>
+      </c>
+      <c r="J302" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10">
+      <c r="A303">
+        <v>1614</v>
+      </c>
+      <c r="B303">
+        <v>9521289</v>
+      </c>
+      <c r="C303">
+        <v>156</v>
+      </c>
+      <c r="D303">
+        <v>120</v>
+      </c>
+      <c r="E303">
+        <v>87</v>
+      </c>
+      <c r="F303">
+        <v>206</v>
+      </c>
+      <c r="G303">
+        <v>357</v>
+      </c>
+      <c r="H303">
+        <v>1016</v>
+      </c>
+      <c r="I303">
+        <v>659</v>
+      </c>
+      <c r="J303" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10">
+      <c r="A304">
+        <v>2021</v>
+      </c>
+      <c r="B304">
+        <v>8743458</v>
+      </c>
+      <c r="C304">
+        <v>147</v>
+      </c>
+      <c r="D304">
+        <v>115</v>
+      </c>
+      <c r="E304">
+        <v>89</v>
+      </c>
+      <c r="F304">
+        <v>203</v>
+      </c>
+      <c r="G304">
+        <v>342</v>
+      </c>
+      <c r="H304">
+        <v>-162.5</v>
+      </c>
+      <c r="I304">
+        <v>-504.5</v>
+      </c>
+      <c r="J304" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10">
+      <c r="A305">
+        <v>449</v>
+      </c>
+      <c r="B305">
+        <v>1283595</v>
+      </c>
+      <c r="C305">
+        <v>174</v>
+      </c>
+      <c r="D305">
+        <v>127</v>
+      </c>
+      <c r="E305">
+        <v>37</v>
+      </c>
+      <c r="F305">
+        <v>163</v>
+      </c>
+      <c r="G305">
+        <v>378</v>
+      </c>
+      <c r="H305">
+        <v>1660</v>
+      </c>
+      <c r="I305">
+        <v>1282</v>
+      </c>
+      <c r="J305" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10">
+      <c r="A306">
+        <v>1545</v>
+      </c>
+      <c r="B306">
+        <v>9006224</v>
+      </c>
+      <c r="C306">
+        <v>151</v>
+      </c>
+      <c r="D306">
+        <v>130</v>
+      </c>
+      <c r="E306">
+        <v>86</v>
+      </c>
+      <c r="F306">
+        <v>215</v>
+      </c>
+      <c r="G306">
+        <v>387</v>
+      </c>
+      <c r="H306">
+        <v>1448</v>
+      </c>
+      <c r="I306">
+        <v>1061</v>
+      </c>
+      <c r="J306" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10">
+      <c r="A307">
+        <v>1944</v>
+      </c>
+      <c r="B307">
+        <v>5875134</v>
+      </c>
+      <c r="C307">
+        <v>207</v>
+      </c>
+      <c r="D307">
+        <v>116</v>
+      </c>
+      <c r="E307">
+        <v>80</v>
+      </c>
+      <c r="F307">
+        <v>195</v>
+      </c>
+      <c r="G307">
+        <v>345</v>
+      </c>
+      <c r="H307">
+        <v>1532.5</v>
+      </c>
+      <c r="I307">
+        <v>1187.5</v>
+      </c>
+      <c r="J307" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10">
+      <c r="A308">
+        <v>1634</v>
+      </c>
+      <c r="B308">
+        <v>9563555</v>
+      </c>
+      <c r="C308">
+        <v>199</v>
+      </c>
+      <c r="D308">
+        <v>184</v>
+      </c>
+      <c r="E308">
+        <v>1</v>
+      </c>
+      <c r="F308">
+        <v>184</v>
+      </c>
+      <c r="G308">
+        <v>457.5</v>
+      </c>
+      <c r="H308">
+        <v>-170</v>
+      </c>
+      <c r="I308">
+        <v>-627.5</v>
+      </c>
+      <c r="J308" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10">
+      <c r="A309">
+        <v>1899</v>
+      </c>
+      <c r="B309">
+        <v>8654236</v>
+      </c>
+      <c r="C309">
+        <v>197</v>
+      </c>
+      <c r="D309">
+        <v>188</v>
+      </c>
+      <c r="E309">
+        <v>1</v>
+      </c>
+      <c r="F309">
+        <v>188</v>
+      </c>
+      <c r="G309">
+        <v>467.5</v>
+      </c>
+      <c r="H309">
+        <v>-115</v>
+      </c>
+      <c r="I309">
+        <v>-582.5</v>
+      </c>
+      <c r="J309" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10">
+      <c r="A310">
+        <v>1476</v>
+      </c>
+      <c r="B310">
+        <v>9003758</v>
+      </c>
+      <c r="C310">
+        <v>191</v>
+      </c>
+      <c r="D310">
+        <v>186</v>
+      </c>
+      <c r="E310">
+        <v>1</v>
+      </c>
+      <c r="F310">
+        <v>186</v>
+      </c>
+      <c r="G310">
+        <v>462.5</v>
+      </c>
+      <c r="H310">
+        <v>-10</v>
+      </c>
+      <c r="I310">
+        <v>-472.5</v>
+      </c>
+      <c r="J310" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10">
+      <c r="A311">
+        <v>336</v>
+      </c>
+      <c r="B311">
+        <v>5814700</v>
+      </c>
+      <c r="C311">
+        <v>163</v>
+      </c>
+      <c r="D311">
+        <v>123</v>
+      </c>
+      <c r="E311">
+        <v>34</v>
+      </c>
+      <c r="F311">
+        <v>156</v>
+      </c>
+      <c r="G311">
+        <v>366</v>
+      </c>
+      <c r="H311">
+        <v>855</v>
+      </c>
+      <c r="I311">
+        <v>489</v>
+      </c>
+      <c r="J311" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10">
+      <c r="A312">
+        <v>170</v>
+      </c>
+      <c r="B312">
+        <v>5639011</v>
+      </c>
+      <c r="C312">
+        <v>166</v>
+      </c>
+      <c r="D312">
+        <v>126</v>
+      </c>
+      <c r="E312">
+        <v>30</v>
+      </c>
+      <c r="F312">
+        <v>155</v>
+      </c>
+      <c r="G312">
+        <v>375</v>
+      </c>
+      <c r="H312">
+        <v>822.5</v>
+      </c>
+      <c r="I312">
+        <v>447.5</v>
+      </c>
+      <c r="J312" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10">
+      <c r="A313">
+        <v>391</v>
+      </c>
+      <c r="B313">
+        <v>539318</v>
+      </c>
+      <c r="C313">
+        <v>157</v>
+      </c>
+      <c r="D313">
+        <v>130</v>
+      </c>
+      <c r="E313">
+        <v>18</v>
+      </c>
+      <c r="F313">
+        <v>147</v>
+      </c>
+      <c r="G313">
+        <v>387</v>
+      </c>
+      <c r="H313">
+        <v>1027.8</v>
+      </c>
+      <c r="I313">
+        <v>640.8</v>
+      </c>
+      <c r="J313" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10">
+      <c r="A314">
+        <v>557</v>
+      </c>
+      <c r="B314">
+        <v>4190994</v>
+      </c>
+      <c r="C314">
+        <v>182</v>
+      </c>
+      <c r="D314">
+        <v>173</v>
+      </c>
+      <c r="E314">
+        <v>1</v>
+      </c>
+      <c r="F314">
+        <v>173</v>
+      </c>
+      <c r="G314">
+        <v>430</v>
+      </c>
+      <c r="H314">
+        <v>-197.5</v>
+      </c>
+      <c r="I314">
+        <v>-627.5</v>
+      </c>
+      <c r="J314" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10">
+      <c r="A315">
+        <v>505</v>
+      </c>
+      <c r="B315">
+        <v>3425505</v>
+      </c>
+      <c r="C315">
+        <v>152</v>
+      </c>
+      <c r="D315">
+        <v>122</v>
+      </c>
+      <c r="E315">
+        <v>18</v>
+      </c>
+      <c r="F315">
+        <v>139</v>
+      </c>
+      <c r="G315">
+        <v>363</v>
+      </c>
+      <c r="H315">
+        <v>109</v>
+      </c>
+      <c r="I315">
+        <v>-254</v>
+      </c>
+      <c r="J315" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10">
+      <c r="A316">
+        <v>1741</v>
+      </c>
+      <c r="B316">
+        <v>9744561</v>
+      </c>
+      <c r="C316">
+        <v>168</v>
+      </c>
+      <c r="D316">
+        <v>119</v>
+      </c>
+      <c r="E316">
+        <v>36</v>
+      </c>
+      <c r="F316">
+        <v>154</v>
+      </c>
+      <c r="G316">
+        <v>354</v>
+      </c>
+      <c r="H316">
+        <v>1143.9</v>
+      </c>
+      <c r="I316">
+        <v>789.9</v>
+      </c>
+      <c r="J316" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10">
+      <c r="A317">
+        <v>1040</v>
+      </c>
+      <c r="B317">
+        <v>8621411</v>
+      </c>
+      <c r="C317">
+        <v>148</v>
+      </c>
+      <c r="D317">
+        <v>109</v>
+      </c>
+      <c r="E317">
+        <v>78</v>
+      </c>
+      <c r="F317">
+        <v>186</v>
+      </c>
+      <c r="G317">
+        <v>324</v>
+      </c>
+      <c r="H317">
+        <v>1478</v>
+      </c>
+      <c r="I317">
+        <v>1154</v>
+      </c>
+      <c r="J317" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10">
+      <c r="A318">
+        <v>1120</v>
+      </c>
+      <c r="B318">
+        <v>8384371</v>
+      </c>
+      <c r="C318">
+        <v>170</v>
+      </c>
+      <c r="D318">
+        <v>117</v>
+      </c>
+      <c r="E318">
+        <v>93</v>
+      </c>
+      <c r="F318">
+        <v>209</v>
+      </c>
+      <c r="G318">
+        <v>348</v>
+      </c>
+      <c r="H318">
+        <v>942</v>
+      </c>
+      <c r="I318">
+        <v>594</v>
+      </c>
+      <c r="J318" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10">
+      <c r="A319">
+        <v>559</v>
+      </c>
+      <c r="B319">
+        <v>2977144</v>
+      </c>
+      <c r="C319">
+        <v>192</v>
+      </c>
+      <c r="D319">
+        <v>183</v>
+      </c>
+      <c r="E319">
+        <v>1</v>
+      </c>
+      <c r="F319">
+        <v>183</v>
+      </c>
+      <c r="G319">
+        <v>455</v>
+      </c>
+      <c r="H319">
+        <v>-340</v>
+      </c>
+      <c r="I319">
+        <v>-795</v>
+      </c>
+      <c r="J319" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10">
+      <c r="A320">
+        <v>1687</v>
+      </c>
+      <c r="B320">
+        <v>9648870</v>
+      </c>
+      <c r="C320">
+        <v>157</v>
+      </c>
+      <c r="D320">
+        <v>122</v>
+      </c>
+      <c r="E320">
+        <v>24</v>
+      </c>
+      <c r="F320">
+        <v>145</v>
+      </c>
+      <c r="G320">
+        <v>363</v>
+      </c>
+      <c r="H320">
+        <v>-117.5</v>
+      </c>
+      <c r="I320">
+        <v>-480.5</v>
+      </c>
+      <c r="J320" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10">
+      <c r="A321">
+        <v>974</v>
+      </c>
+      <c r="B321">
+        <v>8295294</v>
+      </c>
+      <c r="C321">
+        <v>190</v>
+      </c>
+      <c r="D321">
+        <v>182</v>
+      </c>
+      <c r="E321">
+        <v>1</v>
+      </c>
+      <c r="F321">
+        <v>182</v>
+      </c>
+      <c r="G321">
+        <v>452.5</v>
+      </c>
+      <c r="H321">
+        <v>-157.5</v>
+      </c>
+      <c r="I321">
+        <v>-610</v>
+      </c>
+      <c r="J321" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10">
+      <c r="A322">
+        <v>97</v>
+      </c>
+      <c r="B322">
+        <v>1435212</v>
+      </c>
+      <c r="C322">
+        <v>256</v>
+      </c>
+      <c r="D322">
+        <v>191</v>
+      </c>
+      <c r="E322">
+        <v>32</v>
+      </c>
+      <c r="F322">
+        <v>222</v>
+      </c>
+      <c r="G322">
+        <v>380</v>
+      </c>
+      <c r="H322">
+        <v>952.3</v>
+      </c>
+      <c r="I322">
+        <v>572.3</v>
+      </c>
+      <c r="J322" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10">
+      <c r="A323">
+        <v>730</v>
+      </c>
+      <c r="B323">
+        <v>6111301</v>
+      </c>
+      <c r="C323">
+        <v>191</v>
+      </c>
+      <c r="D323">
+        <v>189</v>
+      </c>
+      <c r="E323">
+        <v>1</v>
+      </c>
+      <c r="F323">
+        <v>189</v>
+      </c>
+      <c r="G323">
+        <v>470</v>
+      </c>
+      <c r="H323">
+        <v>0</v>
+      </c>
+      <c r="I323">
+        <v>-470</v>
+      </c>
+      <c r="J323" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10">
+      <c r="A324">
+        <v>7</v>
+      </c>
+      <c r="B324">
+        <v>5824650</v>
+      </c>
+      <c r="C324">
+        <v>161</v>
+      </c>
+      <c r="D324">
+        <v>117</v>
+      </c>
+      <c r="E324">
+        <v>31</v>
+      </c>
+      <c r="F324">
+        <v>147</v>
+      </c>
+      <c r="G324">
+        <v>348</v>
+      </c>
+      <c r="H324">
+        <v>1018.8</v>
+      </c>
+      <c r="I324">
+        <v>670.8</v>
+      </c>
+      <c r="J324" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10">
+      <c r="A325">
+        <v>973</v>
+      </c>
+      <c r="B325">
+        <v>8621890</v>
+      </c>
+      <c r="C325">
+        <v>202</v>
+      </c>
+      <c r="D325">
+        <v>187</v>
+      </c>
+      <c r="E325">
+        <v>1</v>
+      </c>
+      <c r="F325">
+        <v>187</v>
+      </c>
+      <c r="G325">
+        <v>465</v>
+      </c>
+      <c r="H325">
+        <v>-353.292</v>
+      </c>
+      <c r="I325">
+        <v>-818.292</v>
+      </c>
+      <c r="J325" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10">
+      <c r="A326">
+        <v>1625</v>
+      </c>
+      <c r="B326">
+        <v>9540871</v>
+      </c>
+      <c r="C326">
+        <v>198</v>
+      </c>
+      <c r="D326">
+        <v>176</v>
+      </c>
+      <c r="E326">
+        <v>1</v>
+      </c>
+      <c r="F326">
+        <v>176</v>
+      </c>
+      <c r="G326">
+        <v>437.5</v>
+      </c>
+      <c r="H326">
+        <v>-400.681</v>
+      </c>
+      <c r="I326">
+        <v>-838.181</v>
+      </c>
+      <c r="J326" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10">
+      <c r="A327">
+        <v>341</v>
+      </c>
+      <c r="B327">
+        <v>5966316</v>
+      </c>
+      <c r="C327">
+        <v>204</v>
+      </c>
+      <c r="D327">
+        <v>177</v>
+      </c>
+      <c r="E327">
+        <v>1</v>
+      </c>
+      <c r="F327">
+        <v>177</v>
+      </c>
+      <c r="G327">
+        <v>440</v>
+      </c>
+      <c r="H327">
+        <v>-247.5</v>
+      </c>
+      <c r="I327">
+        <v>-687.5</v>
+      </c>
+      <c r="J327" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10">
+      <c r="A328">
+        <v>1132</v>
+      </c>
+      <c r="B328">
+        <v>8670226</v>
+      </c>
+      <c r="C328">
+        <v>158</v>
+      </c>
+      <c r="D328">
+        <v>126</v>
+      </c>
+      <c r="E328">
+        <v>24</v>
+      </c>
+      <c r="F328">
+        <v>149</v>
+      </c>
+      <c r="G328">
+        <v>375</v>
+      </c>
+      <c r="H328">
+        <v>989</v>
+      </c>
+      <c r="I328">
+        <v>614</v>
+      </c>
+      <c r="J328" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10">
+      <c r="A329">
+        <v>1713</v>
+      </c>
+      <c r="B329">
+        <v>9685687</v>
+      </c>
+      <c r="C329">
+        <v>198</v>
+      </c>
+      <c r="D329">
+        <v>197</v>
+      </c>
+      <c r="E329">
+        <v>1</v>
+      </c>
+      <c r="F329">
+        <v>197</v>
+      </c>
+      <c r="G329">
+        <v>490</v>
+      </c>
+      <c r="H329">
+        <v>-164.037</v>
+      </c>
+      <c r="I329">
+        <v>-654.037</v>
+      </c>
+      <c r="J329" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10">
+      <c r="A330">
+        <v>1005</v>
+      </c>
+      <c r="B330">
+        <v>8839356</v>
+      </c>
+      <c r="C330">
+        <v>144</v>
+      </c>
+      <c r="D330">
+        <v>116</v>
+      </c>
+      <c r="E330">
+        <v>27</v>
+      </c>
+      <c r="F330">
+        <v>142</v>
+      </c>
+      <c r="G330">
+        <v>345</v>
+      </c>
+      <c r="H330">
+        <v>860.26</v>
+      </c>
+      <c r="I330">
+        <v>515.26</v>
+      </c>
+      <c r="J330" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10">
+      <c r="A331">
+        <v>1161</v>
+      </c>
+      <c r="B331">
+        <v>8570577</v>
+      </c>
+      <c r="C331">
+        <v>200</v>
+      </c>
+      <c r="D331">
+        <v>185</v>
+      </c>
+      <c r="E331">
+        <v>1</v>
+      </c>
+      <c r="F331">
+        <v>185</v>
+      </c>
+      <c r="G331">
+        <v>460</v>
+      </c>
+      <c r="H331">
+        <v>-170</v>
+      </c>
+      <c r="I331">
+        <v>-630</v>
+      </c>
+      <c r="J331" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10">
+      <c r="A332">
+        <v>716</v>
+      </c>
+      <c r="B332">
+        <v>6089109</v>
+      </c>
+      <c r="C332">
+        <v>146</v>
+      </c>
+      <c r="D332">
+        <v>128</v>
+      </c>
+      <c r="E332">
+        <v>19</v>
+      </c>
+      <c r="F332">
+        <v>146</v>
+      </c>
+      <c r="G332">
+        <v>381</v>
+      </c>
+      <c r="H332">
+        <v>1373.54</v>
+      </c>
+      <c r="I332">
+        <v>992.54</v>
+      </c>
+      <c r="J332" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10">
+      <c r="A333">
+        <v>1655</v>
+      </c>
+      <c r="B333">
+        <v>9606568</v>
+      </c>
+      <c r="C333">
+        <v>191</v>
+      </c>
+      <c r="D333">
+        <v>185</v>
+      </c>
+      <c r="E333">
+        <v>1</v>
+      </c>
+      <c r="F333">
+        <v>185</v>
+      </c>
+      <c r="G333">
+        <v>460</v>
+      </c>
+      <c r="H333">
+        <v>-200</v>
+      </c>
+      <c r="I333">
+        <v>-660</v>
+      </c>
+      <c r="J333" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10">
+      <c r="A334">
+        <v>88</v>
+      </c>
+      <c r="B334">
+        <v>5250765</v>
+      </c>
+      <c r="C334">
+        <v>186</v>
+      </c>
+      <c r="D334">
+        <v>142</v>
+      </c>
+      <c r="E334">
+        <v>39</v>
+      </c>
+      <c r="F334">
+        <v>180</v>
+      </c>
+      <c r="G334">
+        <v>352.5</v>
+      </c>
+      <c r="H334">
+        <v>-448.169</v>
+      </c>
+      <c r="I334">
+        <v>-800.669</v>
+      </c>
+      <c r="J334" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10">
+      <c r="A335">
+        <v>1867</v>
+      </c>
+      <c r="B335">
+        <v>9963627</v>
+      </c>
+      <c r="C335">
+        <v>162</v>
+      </c>
+      <c r="D335">
+        <v>117</v>
+      </c>
+      <c r="E335">
+        <v>29</v>
+      </c>
+      <c r="F335">
+        <v>145</v>
+      </c>
+      <c r="G335">
+        <v>348</v>
+      </c>
+      <c r="H335">
+        <v>556</v>
+      </c>
+      <c r="I335">
+        <v>208</v>
+      </c>
+      <c r="J335" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10">
+      <c r="A336">
+        <v>791</v>
+      </c>
+      <c r="B336">
+        <v>8886866</v>
+      </c>
+      <c r="C336">
+        <v>279</v>
+      </c>
+      <c r="D336">
+        <v>183</v>
+      </c>
+      <c r="E336">
+        <v>66</v>
+      </c>
+      <c r="F336">
+        <v>248</v>
+      </c>
+      <c r="G336">
+        <v>364</v>
+      </c>
+      <c r="H336">
+        <v>1194.5</v>
+      </c>
+      <c r="I336">
+        <v>830.5</v>
+      </c>
+      <c r="J336" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10">
+      <c r="A337">
+        <v>1939</v>
+      </c>
+      <c r="B337">
+        <v>5022756</v>
+      </c>
+      <c r="C337">
+        <v>158</v>
+      </c>
+      <c r="D337">
+        <v>123</v>
+      </c>
+      <c r="E337">
+        <v>26</v>
+      </c>
+      <c r="F337">
+        <v>148</v>
+      </c>
+      <c r="G337">
+        <v>366</v>
+      </c>
+      <c r="H337">
+        <v>580</v>
+      </c>
+      <c r="I337">
+        <v>214</v>
+      </c>
+      <c r="J337" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10">
+      <c r="A338">
+        <v>289</v>
+      </c>
+      <c r="B338">
+        <v>5672891</v>
+      </c>
+      <c r="C338">
+        <v>158</v>
+      </c>
+      <c r="D338">
+        <v>123</v>
+      </c>
+      <c r="E338">
+        <v>21</v>
+      </c>
+      <c r="F338">
+        <v>143</v>
+      </c>
+      <c r="G338">
+        <v>366</v>
+      </c>
+      <c r="H338">
+        <v>314.5</v>
+      </c>
+      <c r="I338">
+        <v>-51.5</v>
+      </c>
+      <c r="J338" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10">
+      <c r="A339">
+        <v>63</v>
+      </c>
+      <c r="B339">
+        <v>5435964</v>
+      </c>
+      <c r="C339">
+        <v>161</v>
+      </c>
+      <c r="D339">
+        <v>130</v>
+      </c>
+      <c r="E339">
+        <v>90</v>
+      </c>
+      <c r="F339">
+        <v>219</v>
+      </c>
+      <c r="G339">
+        <v>387</v>
+      </c>
+      <c r="H339">
+        <v>184</v>
+      </c>
+      <c r="I339">
+        <v>-203</v>
+      </c>
+      <c r="J339" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10">
+      <c r="A340">
+        <v>626</v>
+      </c>
+      <c r="B340">
+        <v>5793211</v>
+      </c>
+      <c r="C340">
+        <v>160</v>
+      </c>
+      <c r="D340">
+        <v>122</v>
+      </c>
+      <c r="E340">
+        <v>31</v>
+      </c>
+      <c r="F340">
+        <v>152</v>
+      </c>
+      <c r="G340">
+        <v>363</v>
+      </c>
+      <c r="H340">
+        <v>-91</v>
+      </c>
+      <c r="I340">
+        <v>-454</v>
+      </c>
+      <c r="J340" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10">
+      <c r="A341">
+        <v>1123</v>
+      </c>
+      <c r="B341">
+        <v>8442223</v>
+      </c>
+      <c r="C341">
+        <v>134</v>
+      </c>
+      <c r="D341">
+        <v>123</v>
+      </c>
+      <c r="E341">
+        <v>12</v>
+      </c>
+      <c r="F341">
+        <v>134</v>
+      </c>
+      <c r="G341">
+        <v>366</v>
+      </c>
+      <c r="H341">
+        <v>470</v>
+      </c>
+      <c r="I341">
+        <v>104</v>
+      </c>
+      <c r="J341" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10">
+      <c r="A342">
+        <v>1261</v>
+      </c>
+      <c r="B342">
+        <v>8310862</v>
+      </c>
+      <c r="C342">
+        <v>170</v>
+      </c>
+      <c r="D342">
+        <v>165</v>
+      </c>
+      <c r="E342">
+        <v>1</v>
+      </c>
+      <c r="F342">
+        <v>165</v>
+      </c>
+      <c r="G342">
+        <v>410</v>
+      </c>
+      <c r="H342">
+        <v>-200</v>
+      </c>
+      <c r="I342">
+        <v>-610</v>
+      </c>
+      <c r="J342" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10">
+      <c r="A343">
+        <v>263</v>
+      </c>
+      <c r="B343">
+        <v>5653425</v>
+      </c>
+      <c r="C343">
+        <v>166</v>
+      </c>
+      <c r="D343">
+        <v>128</v>
+      </c>
+      <c r="E343">
+        <v>30</v>
+      </c>
+      <c r="F343">
+        <v>157</v>
+      </c>
+      <c r="G343">
+        <v>381</v>
+      </c>
+      <c r="H343">
+        <v>-280.5</v>
+      </c>
+      <c r="I343">
+        <v>-661.5</v>
+      </c>
+      <c r="J343" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10">
+      <c r="A344">
+        <v>1082</v>
+      </c>
+      <c r="B344">
+        <v>6742113</v>
+      </c>
+      <c r="C344">
+        <v>154</v>
+      </c>
+      <c r="D344">
+        <v>125</v>
+      </c>
+      <c r="E344">
+        <v>96</v>
+      </c>
+      <c r="F344">
+        <v>220</v>
+      </c>
+      <c r="G344">
+        <v>372</v>
+      </c>
+      <c r="H344">
+        <v>777.7</v>
+      </c>
+      <c r="I344">
+        <v>405.7</v>
+      </c>
+      <c r="J344" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10">
+      <c r="A345">
+        <v>783</v>
+      </c>
+      <c r="B345">
+        <v>8462272</v>
+      </c>
+      <c r="C345">
+        <v>193</v>
+      </c>
+      <c r="D345">
+        <v>187</v>
+      </c>
+      <c r="E345">
+        <v>1</v>
+      </c>
+      <c r="F345">
+        <v>187</v>
+      </c>
+      <c r="G345">
+        <v>465</v>
+      </c>
+      <c r="H345">
+        <v>-200</v>
+      </c>
+      <c r="I345">
+        <v>-665</v>
+      </c>
+      <c r="J345" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10">
+      <c r="A346">
+        <v>515</v>
+      </c>
+      <c r="B346">
+        <v>5892970</v>
+      </c>
+      <c r="C346">
+        <v>158</v>
+      </c>
+      <c r="D346">
+        <v>158</v>
+      </c>
+      <c r="E346">
+        <v>1</v>
+      </c>
+      <c r="F346">
+        <v>158</v>
+      </c>
+      <c r="G346">
+        <v>392.5</v>
+      </c>
+      <c r="H346">
+        <v>-250</v>
+      </c>
+      <c r="I346">
+        <v>-642.5</v>
+      </c>
+      <c r="J346" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10">
+      <c r="A347">
+        <v>193</v>
+      </c>
+      <c r="B347">
+        <v>5869380</v>
+      </c>
+      <c r="C347">
+        <v>149</v>
+      </c>
+      <c r="D347">
+        <v>127</v>
+      </c>
+      <c r="E347">
+        <v>90</v>
+      </c>
+      <c r="F347">
+        <v>216</v>
+      </c>
+      <c r="G347">
+        <v>378</v>
+      </c>
+      <c r="H347">
+        <v>1511.5</v>
+      </c>
+      <c r="I347">
+        <v>1133.5</v>
+      </c>
+      <c r="J347" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10">
+      <c r="A348">
+        <v>249</v>
+      </c>
+      <c r="B348">
+        <v>5625574</v>
+      </c>
+      <c r="C348">
+        <v>332</v>
+      </c>
+      <c r="D348">
+        <v>183</v>
+      </c>
+      <c r="E348">
+        <v>150</v>
+      </c>
+      <c r="F348">
+        <v>332</v>
+      </c>
+      <c r="G348">
+        <v>364</v>
+      </c>
+      <c r="H348">
+        <v>956</v>
+      </c>
+      <c r="I348">
+        <v>592</v>
+      </c>
+      <c r="J348" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10">
+      <c r="A349">
+        <v>1873</v>
+      </c>
+      <c r="B349">
+        <v>9974456</v>
+      </c>
+      <c r="C349">
+        <v>168</v>
+      </c>
+      <c r="D349">
+        <v>121</v>
+      </c>
+      <c r="E349">
+        <v>41</v>
+      </c>
+      <c r="F349">
+        <v>161</v>
+      </c>
+      <c r="G349">
+        <v>360</v>
+      </c>
+      <c r="H349">
+        <v>774.4</v>
+      </c>
+      <c r="I349">
+        <v>414.4</v>
+      </c>
+      <c r="J349" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10">
+      <c r="A350">
+        <v>1486</v>
+      </c>
+      <c r="B350">
+        <v>6740011</v>
+      </c>
+      <c r="C350">
+        <v>213</v>
+      </c>
+      <c r="D350">
+        <v>202</v>
+      </c>
+      <c r="E350">
+        <v>1</v>
+      </c>
+      <c r="F350">
+        <v>202</v>
+      </c>
+      <c r="G350">
+        <v>502.5</v>
+      </c>
+      <c r="H350">
+        <v>-165</v>
+      </c>
+      <c r="I350">
+        <v>-667.5</v>
+      </c>
+      <c r="J350" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10">
+      <c r="A351">
+        <v>1750</v>
+      </c>
+      <c r="B351">
+        <v>9754706</v>
+      </c>
+      <c r="C351">
+        <v>190</v>
+      </c>
+      <c r="D351">
+        <v>179</v>
+      </c>
+      <c r="E351">
+        <v>1</v>
+      </c>
+      <c r="F351">
+        <v>179</v>
+      </c>
+      <c r="G351">
+        <v>445</v>
+      </c>
+      <c r="H351">
+        <v>-194.738</v>
+      </c>
+      <c r="I351">
+        <v>-639.737</v>
+      </c>
+      <c r="J351" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10">
+      <c r="A352">
+        <v>1808</v>
+      </c>
+      <c r="B352">
+        <v>9844369</v>
+      </c>
+      <c r="C352">
+        <v>202</v>
+      </c>
+      <c r="D352">
+        <v>191</v>
+      </c>
+      <c r="E352">
+        <v>1</v>
+      </c>
+      <c r="F352">
+        <v>191</v>
+      </c>
+      <c r="G352">
+        <v>475</v>
+      </c>
+      <c r="H352">
+        <v>-195.493</v>
+      </c>
+      <c r="I352">
+        <v>-670.4930000000001</v>
+      </c>
+      <c r="J352" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10">
+      <c r="A353">
+        <v>875</v>
+      </c>
+      <c r="B353">
+        <v>8456082</v>
+      </c>
+      <c r="C353">
+        <v>193</v>
+      </c>
+      <c r="D353">
+        <v>185</v>
+      </c>
+      <c r="E353">
+        <v>1</v>
+      </c>
+      <c r="F353">
+        <v>185</v>
+      </c>
+      <c r="G353">
+        <v>460</v>
+      </c>
+      <c r="H353">
+        <v>-229.16</v>
+      </c>
+      <c r="I353">
+        <v>-689.159</v>
+      </c>
+      <c r="J353" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10">
+      <c r="A354">
+        <v>878</v>
+      </c>
+      <c r="B354">
+        <v>6279354</v>
+      </c>
+      <c r="C354">
+        <v>142</v>
+      </c>
+      <c r="D354">
+        <v>118</v>
+      </c>
+      <c r="E354">
+        <v>19</v>
+      </c>
+      <c r="F354">
+        <v>136</v>
+      </c>
+      <c r="G354">
+        <v>351</v>
+      </c>
+      <c r="H354">
+        <v>1132.9</v>
+      </c>
+      <c r="I354">
+        <v>781.9</v>
+      </c>
+      <c r="J354" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10">
+      <c r="A355">
+        <v>932</v>
+      </c>
+      <c r="B355">
+        <v>2424061</v>
+      </c>
+      <c r="C355">
+        <v>145</v>
+      </c>
+      <c r="D355">
+        <v>127</v>
+      </c>
+      <c r="E355">
+        <v>19</v>
+      </c>
+      <c r="F355">
+        <v>145</v>
+      </c>
+      <c r="G355">
+        <v>378</v>
+      </c>
+      <c r="H355">
+        <v>898.14</v>
+      </c>
+      <c r="I355">
+        <v>520.14</v>
+      </c>
+      <c r="J355" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10">
+      <c r="A356">
+        <v>442</v>
+      </c>
+      <c r="B356">
+        <v>4893454</v>
+      </c>
+      <c r="C356">
+        <v>171</v>
+      </c>
+      <c r="D356">
+        <v>123</v>
+      </c>
+      <c r="E356">
+        <v>35</v>
+      </c>
+      <c r="F356">
+        <v>157</v>
+      </c>
+      <c r="G356">
+        <v>366</v>
+      </c>
+      <c r="H356">
+        <v>1482.5</v>
+      </c>
+      <c r="I356">
+        <v>1116.5</v>
+      </c>
+      <c r="J356" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10">
+      <c r="A357">
+        <v>714</v>
+      </c>
+      <c r="B357">
+        <v>6043443</v>
+      </c>
+      <c r="C357">
+        <v>160</v>
+      </c>
+      <c r="D357">
+        <v>126</v>
+      </c>
+      <c r="E357">
+        <v>19</v>
+      </c>
+      <c r="F357">
+        <v>144</v>
+      </c>
+      <c r="G357">
+        <v>375</v>
+      </c>
+      <c r="H357">
+        <v>1500</v>
+      </c>
+      <c r="I357">
+        <v>1125</v>
+      </c>
+      <c r="J357" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10">
+      <c r="A358">
+        <v>286</v>
+      </c>
+      <c r="B358">
+        <v>5629083</v>
+      </c>
+      <c r="C358">
+        <v>149</v>
+      </c>
+      <c r="D358">
+        <v>120</v>
+      </c>
+      <c r="E358">
+        <v>88</v>
+      </c>
+      <c r="F358">
+        <v>207</v>
+      </c>
+      <c r="G358">
+        <v>357</v>
+      </c>
+      <c r="H358">
+        <v>225</v>
+      </c>
+      <c r="I358">
+        <v>-132</v>
+      </c>
+      <c r="J358" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10">
+      <c r="A359">
+        <v>40</v>
+      </c>
+      <c r="B359">
+        <v>5630554</v>
+      </c>
+      <c r="C359">
+        <v>127</v>
+      </c>
+      <c r="D359">
+        <v>116</v>
+      </c>
+      <c r="E359">
+        <v>12</v>
+      </c>
+      <c r="F359">
+        <v>127</v>
+      </c>
+      <c r="G359">
+        <v>345</v>
+      </c>
+      <c r="H359">
+        <v>870.03</v>
+      </c>
+      <c r="I359">
+        <v>525.03</v>
+      </c>
+      <c r="J359" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10">
+      <c r="A360">
+        <v>1250</v>
+      </c>
+      <c r="B360">
+        <v>8523989</v>
+      </c>
+      <c r="C360">
+        <v>145</v>
+      </c>
+      <c r="D360">
+        <v>122</v>
+      </c>
+      <c r="E360">
+        <v>80</v>
+      </c>
+      <c r="F360">
+        <v>201</v>
+      </c>
+      <c r="G360">
+        <v>363</v>
+      </c>
+      <c r="H360">
+        <v>-399.5</v>
+      </c>
+      <c r="I360">
+        <v>-762.5</v>
+      </c>
+      <c r="J360" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10">
+      <c r="A361">
+        <v>126</v>
+      </c>
+      <c r="B361">
+        <v>5314572</v>
+      </c>
+      <c r="C361">
+        <v>205</v>
+      </c>
+      <c r="D361">
+        <v>148</v>
+      </c>
+      <c r="E361">
+        <v>51</v>
+      </c>
+      <c r="F361">
+        <v>198</v>
+      </c>
+      <c r="G361">
+        <v>367.5</v>
+      </c>
+      <c r="H361">
+        <v>-277.5</v>
+      </c>
+      <c r="I361">
+        <v>-645</v>
+      </c>
+      <c r="J361" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10">
+      <c r="A362">
+        <v>1990</v>
+      </c>
+      <c r="B362">
+        <v>6064983</v>
+      </c>
+      <c r="C362">
+        <v>166</v>
+      </c>
+      <c r="D362">
+        <v>119</v>
+      </c>
+      <c r="E362">
+        <v>77</v>
+      </c>
+      <c r="F362">
+        <v>195</v>
+      </c>
+      <c r="G362">
+        <v>354</v>
+      </c>
+      <c r="H362">
+        <v>329</v>
+      </c>
+      <c r="I362">
+        <v>-25</v>
+      </c>
+      <c r="J362" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10">
+      <c r="A363">
+        <v>62</v>
+      </c>
+      <c r="B363">
+        <v>5088325</v>
+      </c>
+      <c r="C363">
+        <v>180</v>
+      </c>
+      <c r="D363">
+        <v>133</v>
+      </c>
+      <c r="E363">
+        <v>33</v>
+      </c>
+      <c r="F363">
+        <v>165</v>
+      </c>
+      <c r="G363">
+        <v>396</v>
+      </c>
+      <c r="H363">
+        <v>-78.5</v>
+      </c>
+      <c r="I363">
+        <v>-474.5</v>
+      </c>
+      <c r="J363" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10">
+      <c r="A364">
+        <v>71</v>
+      </c>
+      <c r="B364">
+        <v>5548802</v>
+      </c>
+      <c r="C364">
+        <v>190</v>
+      </c>
+      <c r="D364">
+        <v>137</v>
+      </c>
+      <c r="E364">
+        <v>50</v>
+      </c>
+      <c r="F364">
+        <v>186</v>
+      </c>
+      <c r="G364">
+        <v>408</v>
+      </c>
+      <c r="H364">
+        <v>730.2</v>
+      </c>
+      <c r="I364">
+        <v>322.2</v>
+      </c>
+      <c r="J364" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10">
+      <c r="A365">
+        <v>107</v>
+      </c>
+      <c r="B365">
+        <v>5027420</v>
+      </c>
+      <c r="C365">
+        <v>188</v>
+      </c>
+      <c r="D365">
+        <v>188</v>
+      </c>
+      <c r="E365">
+        <v>1</v>
+      </c>
+      <c r="F365">
+        <v>188</v>
+      </c>
+      <c r="G365">
+        <v>467.5</v>
+      </c>
+      <c r="H365">
+        <v>-177.5</v>
+      </c>
+      <c r="I365">
+        <v>-645</v>
+      </c>
+      <c r="J365" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10">
+      <c r="A366">
+        <v>1615</v>
+      </c>
+      <c r="B366">
+        <v>9523633</v>
+      </c>
+      <c r="C366">
+        <v>170</v>
+      </c>
+      <c r="D366">
+        <v>122</v>
+      </c>
+      <c r="E366">
+        <v>35</v>
+      </c>
+      <c r="F366">
+        <v>156</v>
+      </c>
+      <c r="G366">
+        <v>363</v>
+      </c>
+      <c r="H366">
+        <v>-390.2</v>
+      </c>
+      <c r="I366">
+        <v>-753.2</v>
+      </c>
+      <c r="J366" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10">
+      <c r="A367">
+        <v>566</v>
+      </c>
+      <c r="B367">
+        <v>4730535</v>
+      </c>
+      <c r="C367">
+        <v>195</v>
+      </c>
+      <c r="D367">
+        <v>173</v>
+      </c>
+      <c r="E367">
+        <v>1</v>
+      </c>
+      <c r="F367">
+        <v>173</v>
+      </c>
+      <c r="G367">
+        <v>430</v>
+      </c>
+      <c r="H367">
+        <v>-230</v>
+      </c>
+      <c r="I367">
+        <v>-660</v>
+      </c>
+      <c r="J367" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10">
+      <c r="A368">
+        <v>157</v>
+      </c>
+      <c r="B368">
+        <v>5024998</v>
+      </c>
+      <c r="C368">
+        <v>145</v>
+      </c>
+      <c r="D368">
+        <v>118</v>
+      </c>
+      <c r="E368">
+        <v>25</v>
+      </c>
+      <c r="F368">
+        <v>142</v>
+      </c>
+      <c r="G368">
+        <v>351</v>
+      </c>
+      <c r="H368">
+        <v>1124.52</v>
+      </c>
+      <c r="I368">
+        <v>773.52</v>
+      </c>
+      <c r="J368" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10">
+      <c r="A369">
+        <v>1984</v>
+      </c>
+      <c r="B369">
+        <v>6002593</v>
+      </c>
+      <c r="C369">
+        <v>153</v>
+      </c>
+      <c r="D369">
+        <v>119</v>
+      </c>
+      <c r="E369">
+        <v>30</v>
+      </c>
+      <c r="F369">
+        <v>148</v>
+      </c>
+      <c r="G369">
+        <v>354</v>
+      </c>
+      <c r="H369">
+        <v>884</v>
+      </c>
+      <c r="I369">
+        <v>530</v>
+      </c>
+      <c r="J369" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10">
+      <c r="A370">
+        <v>1395</v>
+      </c>
+      <c r="B370">
+        <v>5014338</v>
+      </c>
+      <c r="C370">
+        <v>159</v>
+      </c>
+      <c r="D370">
+        <v>123</v>
+      </c>
+      <c r="E370">
+        <v>86</v>
+      </c>
+      <c r="F370">
+        <v>208</v>
+      </c>
+      <c r="G370">
+        <v>366</v>
+      </c>
+      <c r="H370">
+        <v>860.5</v>
+      </c>
+      <c r="I370">
+        <v>494.5</v>
+      </c>
+      <c r="J370" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10">
+      <c r="A371">
+        <v>975</v>
+      </c>
+      <c r="B371">
+        <v>8566129</v>
+      </c>
+      <c r="C371">
+        <v>155</v>
+      </c>
+      <c r="D371">
+        <v>130</v>
+      </c>
+      <c r="E371">
+        <v>91</v>
+      </c>
+      <c r="F371">
+        <v>220</v>
+      </c>
+      <c r="G371">
+        <v>387</v>
+      </c>
+      <c r="H371">
+        <v>-266</v>
+      </c>
+      <c r="I371">
+        <v>-653</v>
+      </c>
+      <c r="J371" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10">
+      <c r="A372">
+        <v>1822</v>
+      </c>
+      <c r="B372">
+        <v>9863719</v>
+      </c>
+      <c r="C372">
+        <v>189</v>
+      </c>
+      <c r="D372">
+        <v>180</v>
+      </c>
+      <c r="E372">
+        <v>1</v>
+      </c>
+      <c r="F372">
+        <v>180</v>
+      </c>
+      <c r="G372">
+        <v>447.5</v>
+      </c>
+      <c r="H372">
+        <v>-217.193</v>
+      </c>
+      <c r="I372">
+        <v>-664.693</v>
+      </c>
+      <c r="J372" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10">
+      <c r="A373">
+        <v>1945</v>
+      </c>
+      <c r="B373">
+        <v>5952669</v>
+      </c>
+      <c r="C373">
+        <v>161</v>
+      </c>
+      <c r="D373">
+        <v>115</v>
+      </c>
+      <c r="E373">
+        <v>37</v>
+      </c>
+      <c r="F373">
+        <v>151</v>
+      </c>
+      <c r="G373">
+        <v>342</v>
+      </c>
+      <c r="H373">
+        <v>1262.5</v>
+      </c>
+      <c r="I373">
+        <v>920.5</v>
+      </c>
+      <c r="J373" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10">
+      <c r="A374">
+        <v>561</v>
+      </c>
+      <c r="B374">
+        <v>2757823</v>
+      </c>
+      <c r="C374">
+        <v>172</v>
+      </c>
+      <c r="D374">
+        <v>131</v>
+      </c>
+      <c r="E374">
+        <v>30</v>
+      </c>
+      <c r="F374">
+        <v>160</v>
+      </c>
+      <c r="G374">
+        <v>390</v>
+      </c>
+      <c r="H374">
+        <v>191.9</v>
+      </c>
+      <c r="I374">
+        <v>-198.1</v>
+      </c>
+      <c r="J374" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10">
+      <c r="A375">
+        <v>1426</v>
+      </c>
+      <c r="B375">
+        <v>8656924</v>
+      </c>
+      <c r="C375">
+        <v>170</v>
+      </c>
+      <c r="D375">
+        <v>128</v>
+      </c>
+      <c r="E375">
+        <v>31</v>
+      </c>
+      <c r="F375">
+        <v>158</v>
+      </c>
+      <c r="G375">
+        <v>381</v>
+      </c>
+      <c r="H375">
+        <v>836.1</v>
+      </c>
+      <c r="I375">
+        <v>455.1</v>
+      </c>
+      <c r="J375" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10">
+      <c r="A376">
+        <v>1551</v>
+      </c>
+      <c r="B376">
+        <v>9421813</v>
+      </c>
+      <c r="C376">
+        <v>185</v>
+      </c>
+      <c r="D376">
+        <v>184</v>
+      </c>
+      <c r="E376">
+        <v>1</v>
+      </c>
+      <c r="F376">
+        <v>184</v>
+      </c>
+      <c r="G376">
+        <v>457.5</v>
+      </c>
+      <c r="H376">
+        <v>0</v>
+      </c>
+      <c r="I376">
+        <v>-457.5</v>
+      </c>
+      <c r="J376" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10">
+      <c r="A377">
+        <v>1969</v>
+      </c>
+      <c r="B377">
+        <v>3123463</v>
+      </c>
+      <c r="C377">
+        <v>156</v>
+      </c>
+      <c r="D377">
+        <v>118</v>
+      </c>
+      <c r="E377">
+        <v>25</v>
+      </c>
+      <c r="F377">
+        <v>142</v>
+      </c>
+      <c r="G377">
+        <v>351</v>
+      </c>
+      <c r="H377">
+        <v>909</v>
+      </c>
+      <c r="I377">
+        <v>558</v>
+      </c>
+      <c r="J377" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10">
+      <c r="A378">
+        <v>1031</v>
+      </c>
+      <c r="B378">
+        <v>8833777</v>
+      </c>
+      <c r="C378">
+        <v>171</v>
+      </c>
+      <c r="D378">
+        <v>129</v>
+      </c>
+      <c r="E378">
+        <v>92</v>
+      </c>
+      <c r="F378">
+        <v>220</v>
+      </c>
+      <c r="G378">
+        <v>384</v>
+      </c>
+      <c r="H378">
+        <v>1113.5</v>
+      </c>
+      <c r="I378">
+        <v>729.5</v>
+      </c>
+      <c r="J378" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10">
+      <c r="A379">
+        <v>1696</v>
+      </c>
+      <c r="B379">
+        <v>9662872</v>
+      </c>
+      <c r="C379">
+        <v>212</v>
+      </c>
+      <c r="D379">
+        <v>146</v>
+      </c>
+      <c r="E379">
+        <v>44</v>
+      </c>
+      <c r="F379">
+        <v>189</v>
+      </c>
+      <c r="G379">
+        <v>362.5</v>
+      </c>
+      <c r="H379">
+        <v>-291.659</v>
+      </c>
+      <c r="I379">
+        <v>-654.159</v>
+      </c>
+      <c r="J379" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10">
+      <c r="A380">
+        <v>1206</v>
+      </c>
+      <c r="B380">
+        <v>8618302</v>
+      </c>
+      <c r="C380">
+        <v>219</v>
+      </c>
+      <c r="D380">
+        <v>200</v>
+      </c>
+      <c r="E380">
+        <v>1</v>
+      </c>
+      <c r="F380">
+        <v>200</v>
+      </c>
+      <c r="G380">
+        <v>497.5</v>
+      </c>
+      <c r="H380">
+        <v>-155</v>
+      </c>
+      <c r="I380">
+        <v>-652.5</v>
+      </c>
+      <c r="J380" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10">
+      <c r="A381">
+        <v>1213</v>
+      </c>
+      <c r="B381">
+        <v>5022511</v>
+      </c>
+      <c r="C381">
+        <v>192</v>
+      </c>
+      <c r="D381">
+        <v>190</v>
+      </c>
+      <c r="E381">
+        <v>1</v>
+      </c>
+      <c r="F381">
+        <v>190</v>
+      </c>
+      <c r="G381">
+        <v>472.5</v>
+      </c>
+      <c r="H381">
+        <v>-192.5</v>
+      </c>
+      <c r="I381">
+        <v>-665</v>
+      </c>
+      <c r="J381" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10">
+      <c r="A382">
+        <v>1118</v>
+      </c>
+      <c r="B382">
+        <v>8504648</v>
+      </c>
+      <c r="C382">
+        <v>194</v>
+      </c>
+      <c r="D382">
+        <v>172</v>
+      </c>
+      <c r="E382">
+        <v>1</v>
+      </c>
+      <c r="F382">
+        <v>172</v>
+      </c>
+      <c r="G382">
+        <v>427.5</v>
+      </c>
+      <c r="H382">
+        <v>-140</v>
+      </c>
+      <c r="I382">
+        <v>-567.5</v>
+      </c>
+      <c r="J382" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10">
+      <c r="A383">
+        <v>364</v>
+      </c>
+      <c r="B383">
+        <v>305343</v>
+      </c>
+      <c r="C383">
+        <v>194</v>
+      </c>
+      <c r="D383">
+        <v>181</v>
+      </c>
+      <c r="E383">
+        <v>1</v>
+      </c>
+      <c r="F383">
+        <v>181</v>
+      </c>
+      <c r="G383">
+        <v>450</v>
+      </c>
+      <c r="H383">
+        <v>-207.049</v>
+      </c>
+      <c r="I383">
+        <v>-657.049</v>
+      </c>
+      <c r="J383" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10">
+      <c r="A384">
+        <v>1355</v>
+      </c>
+      <c r="B384">
+        <v>3399551</v>
+      </c>
+      <c r="C384">
+        <v>123</v>
+      </c>
+      <c r="D384">
+        <v>86</v>
+      </c>
+      <c r="E384">
+        <v>38</v>
+      </c>
+      <c r="F384">
+        <v>123</v>
+      </c>
+      <c r="G384">
+        <v>255</v>
+      </c>
+      <c r="H384">
+        <v>1695.5</v>
+      </c>
+      <c r="I384">
+        <v>1440.5</v>
+      </c>
+      <c r="J384" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10">
+      <c r="A385">
+        <v>551</v>
+      </c>
+      <c r="B385">
+        <v>3099515</v>
+      </c>
+      <c r="C385">
+        <v>190</v>
+      </c>
+      <c r="D385">
+        <v>183</v>
+      </c>
+      <c r="E385">
+        <v>1</v>
+      </c>
+      <c r="F385">
+        <v>183</v>
+      </c>
+      <c r="G385">
+        <v>455</v>
+      </c>
+      <c r="H385">
+        <v>-237.5</v>
+      </c>
+      <c r="I385">
+        <v>-692.5</v>
+      </c>
+      <c r="J385" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10">
+      <c r="A386">
+        <v>1695</v>
+      </c>
+      <c r="B386">
+        <v>9659832</v>
+      </c>
+      <c r="C386">
+        <v>147</v>
+      </c>
+      <c r="D386">
+        <v>124</v>
+      </c>
+      <c r="E386">
+        <v>21</v>
+      </c>
+      <c r="F386">
+        <v>144</v>
+      </c>
+      <c r="G386">
+        <v>369</v>
+      </c>
+      <c r="H386">
+        <v>893.99</v>
+      </c>
+      <c r="I386">
+        <v>524.99</v>
+      </c>
+      <c r="J386" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10">
+      <c r="A387">
+        <v>1214</v>
+      </c>
+      <c r="B387">
+        <v>5025402</v>
+      </c>
+      <c r="C387">
+        <v>181</v>
+      </c>
+      <c r="D387">
+        <v>117</v>
+      </c>
+      <c r="E387">
+        <v>41</v>
+      </c>
+      <c r="F387">
+        <v>157</v>
+      </c>
+      <c r="G387">
+        <v>348</v>
+      </c>
+      <c r="H387">
+        <v>158</v>
+      </c>
+      <c r="I387">
+        <v>-190</v>
+      </c>
+      <c r="J387" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10">
+      <c r="A388">
+        <v>642</v>
+      </c>
+      <c r="B388">
+        <v>5890129</v>
+      </c>
+      <c r="C388">
+        <v>166</v>
+      </c>
+      <c r="D388">
+        <v>112</v>
+      </c>
+      <c r="E388">
+        <v>42</v>
+      </c>
+      <c r="F388">
+        <v>153</v>
+      </c>
+      <c r="G388">
+        <v>333</v>
+      </c>
+      <c r="H388">
+        <v>-320.5</v>
+      </c>
+      <c r="I388">
+        <v>-653.5</v>
+      </c>
+      <c r="J388" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10">
+      <c r="A389">
+        <v>131</v>
+      </c>
+      <c r="B389">
+        <v>5572259</v>
+      </c>
+      <c r="C389">
+        <v>171</v>
+      </c>
+      <c r="D389">
+        <v>129</v>
+      </c>
+      <c r="E389">
+        <v>30</v>
+      </c>
+      <c r="F389">
+        <v>158</v>
+      </c>
+      <c r="G389">
+        <v>384</v>
+      </c>
+      <c r="H389">
+        <v>1404.5</v>
+      </c>
+      <c r="I389">
+        <v>1020.5</v>
+      </c>
+      <c r="J389" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10">
+      <c r="A390">
+        <v>1028</v>
+      </c>
+      <c r="B390">
+        <v>8381753</v>
+      </c>
+      <c r="C390">
+        <v>165</v>
+      </c>
+      <c r="D390">
+        <v>128</v>
+      </c>
+      <c r="E390">
+        <v>27</v>
+      </c>
+      <c r="F390">
+        <v>154</v>
+      </c>
+      <c r="G390">
+        <v>381</v>
+      </c>
+      <c r="H390">
+        <v>-160</v>
+      </c>
+      <c r="I390">
+        <v>-541</v>
+      </c>
+      <c r="J390" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10">
+      <c r="A391">
+        <v>445</v>
+      </c>
+      <c r="B391">
+        <v>1146907</v>
+      </c>
+      <c r="C391">
+        <v>200</v>
+      </c>
+      <c r="D391">
+        <v>184</v>
+      </c>
+      <c r="E391">
+        <v>1</v>
+      </c>
+      <c r="F391">
+        <v>184</v>
+      </c>
+      <c r="G391">
+        <v>457.5</v>
+      </c>
+      <c r="H391">
+        <v>-202.5</v>
+      </c>
+      <c r="I391">
+        <v>-660</v>
+      </c>
+      <c r="J391" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10">
+      <c r="A392">
+        <v>1164</v>
+      </c>
+      <c r="B392">
+        <v>8540379</v>
+      </c>
+      <c r="C392">
+        <v>176</v>
+      </c>
+      <c r="D392">
+        <v>170</v>
+      </c>
+      <c r="E392">
+        <v>1</v>
+      </c>
+      <c r="F392">
+        <v>170</v>
+      </c>
+      <c r="G392">
+        <v>422.5</v>
+      </c>
+      <c r="H392">
+        <v>-182.5</v>
+      </c>
+      <c r="I392">
+        <v>-605</v>
+      </c>
+      <c r="J392" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10">
+      <c r="A393">
+        <v>381</v>
+      </c>
+      <c r="B393">
+        <v>487434</v>
+      </c>
+      <c r="C393">
+        <v>150</v>
+      </c>
+      <c r="D393">
+        <v>119</v>
+      </c>
+      <c r="E393">
+        <v>23</v>
+      </c>
+      <c r="F393">
+        <v>141</v>
+      </c>
+      <c r="G393">
+        <v>354</v>
+      </c>
+      <c r="H393">
+        <v>1568.5</v>
+      </c>
+      <c r="I393">
+        <v>1214.5</v>
+      </c>
+      <c r="J393" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10">
+      <c r="A394">
+        <v>363</v>
+      </c>
+      <c r="B394">
+        <v>2380953</v>
+      </c>
+      <c r="C394">
+        <v>170</v>
+      </c>
+      <c r="D394">
+        <v>120</v>
+      </c>
+      <c r="E394">
+        <v>39</v>
+      </c>
+      <c r="F394">
+        <v>158</v>
+      </c>
+      <c r="G394">
+        <v>357</v>
+      </c>
+      <c r="H394">
+        <v>928</v>
+      </c>
+      <c r="I394">
+        <v>571</v>
+      </c>
+      <c r="J394" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10">
+      <c r="A395">
+        <v>1580</v>
+      </c>
+      <c r="B395">
+        <v>9444634</v>
+      </c>
+      <c r="C395">
+        <v>139</v>
+      </c>
+      <c r="D395">
+        <v>110</v>
+      </c>
+      <c r="E395">
+        <v>26</v>
+      </c>
+      <c r="F395">
+        <v>135</v>
+      </c>
+      <c r="G395">
+        <v>327</v>
+      </c>
+      <c r="H395">
+        <v>-32.04</v>
+      </c>
+      <c r="I395">
+        <v>-359.04</v>
+      </c>
+      <c r="J395" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10">
+      <c r="A396">
+        <v>649</v>
+      </c>
+      <c r="B396">
+        <v>6002406</v>
+      </c>
+      <c r="C396">
+        <v>202</v>
+      </c>
+      <c r="D396">
+        <v>135</v>
+      </c>
+      <c r="E396">
+        <v>19</v>
+      </c>
+      <c r="F396">
+        <v>153</v>
+      </c>
+      <c r="G396">
+        <v>402</v>
+      </c>
+      <c r="H396">
+        <v>817.7</v>
+      </c>
+      <c r="I396">
+        <v>415.7</v>
+      </c>
+      <c r="J396" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10">
+      <c r="A397">
+        <v>219</v>
+      </c>
+      <c r="B397">
+        <v>5574614</v>
+      </c>
+      <c r="C397">
+        <v>150</v>
+      </c>
+      <c r="D397">
+        <v>122</v>
+      </c>
+      <c r="E397">
+        <v>18</v>
+      </c>
+      <c r="F397">
+        <v>139</v>
+      </c>
+      <c r="G397">
+        <v>363</v>
+      </c>
+      <c r="H397">
+        <v>1045.5</v>
+      </c>
+      <c r="I397">
+        <v>682.5</v>
+      </c>
+      <c r="J397" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10">
+      <c r="A398">
+        <v>784</v>
+      </c>
+      <c r="B398">
+        <v>8324063</v>
+      </c>
+      <c r="C398">
+        <v>158</v>
+      </c>
+      <c r="D398">
+        <v>137</v>
+      </c>
+      <c r="E398">
+        <v>87</v>
+      </c>
+      <c r="F398">
+        <v>223</v>
+      </c>
+      <c r="G398">
+        <v>408</v>
+      </c>
+      <c r="H398">
+        <v>328.5</v>
+      </c>
+      <c r="I398">
+        <v>-79.5</v>
+      </c>
+      <c r="J398" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10">
+      <c r="A399">
+        <v>1823</v>
+      </c>
+      <c r="B399">
+        <v>9863749</v>
+      </c>
+      <c r="C399">
+        <v>183</v>
+      </c>
+      <c r="D399">
+        <v>118</v>
+      </c>
+      <c r="E399">
+        <v>57</v>
+      </c>
+      <c r="F399">
+        <v>174</v>
+      </c>
+      <c r="G399">
+        <v>351</v>
+      </c>
+      <c r="H399">
+        <v>451.5</v>
+      </c>
+      <c r="I399">
+        <v>100.5</v>
+      </c>
+      <c r="J399" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10">
+      <c r="A400">
+        <v>966</v>
+      </c>
+      <c r="B400">
+        <v>8454602</v>
+      </c>
+      <c r="C400">
+        <v>149</v>
+      </c>
+      <c r="D400">
+        <v>121</v>
+      </c>
+      <c r="E400">
+        <v>85</v>
+      </c>
+      <c r="F400">
+        <v>205</v>
+      </c>
+      <c r="G400">
+        <v>360</v>
+      </c>
+      <c r="H400">
+        <v>1490.5</v>
+      </c>
+      <c r="I400">
+        <v>1130.5</v>
+      </c>
+      <c r="J400" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10">
+      <c r="A401">
+        <v>321</v>
+      </c>
+      <c r="B401">
+        <v>5795687</v>
+      </c>
+      <c r="C401">
+        <v>158</v>
+      </c>
+      <c r="D401">
+        <v>129</v>
+      </c>
+      <c r="E401">
+        <v>94</v>
+      </c>
+      <c r="F401">
+        <v>222</v>
+      </c>
+      <c r="G401">
+        <v>384</v>
+      </c>
+      <c r="H401">
+        <v>582.5</v>
+      </c>
+      <c r="I401">
+        <v>198.5</v>
+      </c>
+      <c r="J401" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10">
+      <c r="A402">
+        <v>1309</v>
+      </c>
+      <c r="B402">
+        <v>6738942</v>
+      </c>
+      <c r="C402">
+        <v>150</v>
+      </c>
+      <c r="D402">
+        <v>125</v>
+      </c>
+      <c r="E402">
+        <v>84</v>
+      </c>
+      <c r="F402">
+        <v>208</v>
+      </c>
+      <c r="G402">
+        <v>372</v>
+      </c>
+      <c r="H402">
+        <v>1487</v>
+      </c>
+      <c r="I402">
+        <v>1115</v>
+      </c>
+      <c r="J402" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10">
+      <c r="A403">
+        <v>1496</v>
+      </c>
+      <c r="B403">
+        <v>6740186</v>
+      </c>
+      <c r="C403">
+        <v>166</v>
+      </c>
+      <c r="D403">
+        <v>127</v>
+      </c>
+      <c r="E403">
+        <v>25</v>
+      </c>
+      <c r="F403">
+        <v>151</v>
+      </c>
+      <c r="G403">
+        <v>378</v>
+      </c>
+      <c r="H403">
+        <v>1542</v>
+      </c>
+      <c r="I403">
+        <v>1164</v>
+      </c>
+      <c r="J403" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10">
+      <c r="A404">
+        <v>1171</v>
+      </c>
+      <c r="B404">
+        <v>8920671</v>
+      </c>
+      <c r="C404">
+        <v>186</v>
+      </c>
+      <c r="D404">
+        <v>179</v>
+      </c>
+      <c r="E404">
+        <v>1</v>
+      </c>
+      <c r="F404">
+        <v>179</v>
+      </c>
+      <c r="G404">
+        <v>445</v>
+      </c>
+      <c r="H404">
+        <v>-210</v>
+      </c>
+      <c r="I404">
+        <v>-655</v>
+      </c>
+      <c r="J404" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10">
+      <c r="A405">
+        <v>1447</v>
+      </c>
+      <c r="B405">
+        <v>9006753</v>
+      </c>
+      <c r="C405">
+        <v>153</v>
+      </c>
+      <c r="D405">
+        <v>120</v>
+      </c>
+      <c r="E405">
+        <v>87</v>
+      </c>
+      <c r="F405">
+        <v>206</v>
+      </c>
+      <c r="G405">
+        <v>357</v>
+      </c>
+      <c r="H405">
+        <v>-290</v>
+      </c>
+      <c r="I405">
+        <v>-647</v>
+      </c>
+      <c r="J405" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10">
+      <c r="A406">
+        <v>664</v>
+      </c>
+      <c r="B406">
+        <v>6022586</v>
+      </c>
+      <c r="C406">
+        <v>165</v>
+      </c>
+      <c r="D406">
+        <v>124</v>
+      </c>
+      <c r="E406">
+        <v>34</v>
+      </c>
+      <c r="F406">
+        <v>157</v>
+      </c>
+      <c r="G406">
+        <v>369</v>
+      </c>
+      <c r="H406">
+        <v>1051.1</v>
+      </c>
+      <c r="I406">
+        <v>682.1</v>
+      </c>
+      <c r="J406" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10">
+      <c r="A407">
+        <v>1116</v>
+      </c>
+      <c r="B407">
+        <v>8785049</v>
+      </c>
+      <c r="C407">
+        <v>165</v>
+      </c>
+      <c r="D407">
+        <v>119</v>
+      </c>
+      <c r="E407">
+        <v>40</v>
+      </c>
+      <c r="F407">
+        <v>158</v>
+      </c>
+      <c r="G407">
+        <v>354</v>
+      </c>
+      <c r="H407">
+        <v>-347.5</v>
+      </c>
+      <c r="I407">
+        <v>-701.5</v>
+      </c>
+      <c r="J407" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10">
+      <c r="A408">
+        <v>150</v>
+      </c>
+      <c r="B408">
+        <v>5550778</v>
+      </c>
+      <c r="C408">
+        <v>199</v>
+      </c>
+      <c r="D408">
+        <v>186</v>
+      </c>
+      <c r="E408">
+        <v>1</v>
+      </c>
+      <c r="F408">
+        <v>186</v>
+      </c>
+      <c r="G408">
+        <v>462.5</v>
+      </c>
+      <c r="H408">
+        <v>-197.5</v>
+      </c>
+      <c r="I408">
+        <v>-660</v>
+      </c>
+      <c r="J408" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10">
+      <c r="A409">
+        <v>1935</v>
+      </c>
+      <c r="B409">
+        <v>5700228</v>
+      </c>
+      <c r="C409">
+        <v>153</v>
+      </c>
+      <c r="D409">
+        <v>118</v>
+      </c>
+      <c r="E409">
+        <v>28</v>
+      </c>
+      <c r="F409">
+        <v>145</v>
+      </c>
+      <c r="G409">
+        <v>351</v>
+      </c>
+      <c r="H409">
+        <v>1467.5</v>
+      </c>
+      <c r="I409">
+        <v>1116.5</v>
+      </c>
+      <c r="J409" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10">
+      <c r="A410">
+        <v>109</v>
+      </c>
+      <c r="B410">
+        <v>5366541</v>
+      </c>
+      <c r="C410">
+        <v>189</v>
+      </c>
+      <c r="D410">
+        <v>141</v>
+      </c>
+      <c r="E410">
+        <v>29</v>
+      </c>
+      <c r="F410">
+        <v>169</v>
+      </c>
+      <c r="G410">
+        <v>350</v>
+      </c>
+      <c r="H410">
+        <v>-247.628</v>
+      </c>
+      <c r="I410">
+        <v>-597.628</v>
+      </c>
+      <c r="J410" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10">
+      <c r="A411">
+        <v>1489</v>
+      </c>
+      <c r="B411">
+        <v>6740027</v>
+      </c>
+      <c r="C411">
+        <v>156</v>
+      </c>
+      <c r="D411">
+        <v>126</v>
+      </c>
+      <c r="E411">
+        <v>84</v>
+      </c>
+      <c r="F411">
+        <v>209</v>
+      </c>
+      <c r="G411">
+        <v>375</v>
+      </c>
+      <c r="H411">
+        <v>118</v>
+      </c>
+      <c r="I411">
+        <v>-257</v>
+      </c>
+      <c r="J411" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10">
+      <c r="A412">
+        <v>1307</v>
+      </c>
+      <c r="B412">
+        <v>8543518</v>
+      </c>
+      <c r="C412">
+        <v>195</v>
+      </c>
+      <c r="D412">
+        <v>189</v>
+      </c>
+      <c r="E412">
+        <v>1</v>
+      </c>
+      <c r="F412">
+        <v>189</v>
+      </c>
+      <c r="G412">
+        <v>470</v>
+      </c>
+      <c r="H412">
+        <v>-142.514</v>
+      </c>
+      <c r="I412">
+        <v>-612.513</v>
+      </c>
+      <c r="J412" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10">
+      <c r="A413">
+        <v>1971</v>
+      </c>
+      <c r="B413">
+        <v>3168798</v>
+      </c>
+      <c r="C413">
+        <v>159</v>
+      </c>
+      <c r="D413">
+        <v>121</v>
+      </c>
+      <c r="E413">
+        <v>27</v>
+      </c>
+      <c r="F413">
+        <v>147</v>
+      </c>
+      <c r="G413">
+        <v>360</v>
+      </c>
+      <c r="H413">
+        <v>374</v>
+      </c>
+      <c r="I413">
+        <v>14</v>
+      </c>
+      <c r="J413" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10">
+      <c r="A414">
+        <v>686</v>
+      </c>
+      <c r="B414">
+        <v>6098094</v>
+      </c>
+      <c r="C414">
+        <v>192</v>
+      </c>
+      <c r="D414">
+        <v>167</v>
+      </c>
+      <c r="E414">
+        <v>21</v>
+      </c>
+      <c r="F414">
+        <v>187</v>
+      </c>
+      <c r="G414">
+        <v>415</v>
+      </c>
+      <c r="H414">
+        <v>-252.5</v>
+      </c>
+      <c r="I414">
+        <v>-667.5</v>
+      </c>
+      <c r="J414" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10">
+      <c r="A415">
+        <v>1100</v>
+      </c>
+      <c r="B415">
+        <v>6737524</v>
+      </c>
+      <c r="C415">
+        <v>174</v>
+      </c>
+      <c r="D415">
+        <v>133</v>
+      </c>
+      <c r="E415">
+        <v>30</v>
+      </c>
+      <c r="F415">
+        <v>162</v>
+      </c>
+      <c r="G415">
+        <v>396</v>
+      </c>
+      <c r="H415">
+        <v>136</v>
+      </c>
+      <c r="I415">
+        <v>-260</v>
+      </c>
+      <c r="J415" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10">
+      <c r="A416">
+        <v>1</v>
+      </c>
+      <c r="B416">
+        <v>5253702</v>
+      </c>
+      <c r="C416">
+        <v>188</v>
+      </c>
+      <c r="D416">
+        <v>178</v>
+      </c>
+      <c r="E416">
+        <v>1</v>
+      </c>
+      <c r="F416">
+        <v>178</v>
+      </c>
+      <c r="G416">
+        <v>442.5</v>
+      </c>
+      <c r="H416">
+        <v>-260</v>
+      </c>
+      <c r="I416">
+        <v>-702.5</v>
+      </c>
+      <c r="J416" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10">
+      <c r="A417">
+        <v>621</v>
+      </c>
+      <c r="B417">
+        <v>4788416</v>
+      </c>
+      <c r="C417">
+        <v>204</v>
+      </c>
+      <c r="D417">
+        <v>182</v>
+      </c>
+      <c r="E417">
+        <v>1</v>
+      </c>
+      <c r="F417">
+        <v>182</v>
+      </c>
+      <c r="G417">
+        <v>452.5</v>
+      </c>
+      <c r="H417">
+        <v>-210</v>
+      </c>
+      <c r="I417">
+        <v>-662.5</v>
+      </c>
+      <c r="J417" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10">
+      <c r="A418">
+        <v>693</v>
+      </c>
+      <c r="B418">
+        <v>3971852</v>
+      </c>
+      <c r="C418">
+        <v>152</v>
+      </c>
+      <c r="D418">
+        <v>123</v>
+      </c>
+      <c r="E418">
+        <v>21</v>
+      </c>
+      <c r="F418">
+        <v>143</v>
+      </c>
+      <c r="G418">
+        <v>366</v>
+      </c>
+      <c r="H418">
+        <v>481</v>
+      </c>
+      <c r="I418">
+        <v>115</v>
+      </c>
+      <c r="J418" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10">
+      <c r="A419">
+        <v>1131</v>
+      </c>
+      <c r="B419">
+        <v>8343755</v>
+      </c>
+      <c r="C419">
+        <v>148</v>
+      </c>
+      <c r="D419">
+        <v>123</v>
+      </c>
+      <c r="E419">
+        <v>85</v>
+      </c>
+      <c r="F419">
+        <v>207</v>
+      </c>
+      <c r="G419">
+        <v>366</v>
+      </c>
+      <c r="H419">
+        <v>-403</v>
+      </c>
+      <c r="I419">
+        <v>-769</v>
+      </c>
+      <c r="J419" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10">
+      <c r="A420">
+        <v>940</v>
+      </c>
+      <c r="B420">
+        <v>8762093</v>
+      </c>
+      <c r="C420">
+        <v>141</v>
+      </c>
+      <c r="D420">
+        <v>113</v>
+      </c>
+      <c r="E420">
+        <v>77</v>
+      </c>
+      <c r="F420">
+        <v>189</v>
+      </c>
+      <c r="G420">
+        <v>336</v>
+      </c>
+      <c r="H420">
+        <v>858.5</v>
+      </c>
+      <c r="I420">
+        <v>522.5</v>
+      </c>
+      <c r="J420" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10">
+      <c r="A421">
+        <v>675</v>
+      </c>
+      <c r="B421">
+        <v>6064661</v>
+      </c>
+      <c r="C421">
+        <v>150</v>
+      </c>
+      <c r="D421">
+        <v>120</v>
+      </c>
+      <c r="E421">
+        <v>29</v>
+      </c>
+      <c r="F421">
+        <v>148</v>
+      </c>
+      <c r="G421">
+        <v>357</v>
+      </c>
+      <c r="H421">
+        <v>-359.45</v>
+      </c>
+      <c r="I421">
+        <v>-716.45</v>
+      </c>
+      <c r="J421" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10">
+      <c r="A422">
+        <v>912</v>
+      </c>
+      <c r="B422">
+        <v>8372909</v>
+      </c>
+      <c r="C422">
+        <v>192</v>
+      </c>
+      <c r="D422">
+        <v>181</v>
+      </c>
+      <c r="E422">
+        <v>1</v>
+      </c>
+      <c r="F422">
+        <v>181</v>
+      </c>
+      <c r="G422">
+        <v>450</v>
+      </c>
+      <c r="H422">
+        <v>-187.5</v>
+      </c>
+      <c r="I422">
+        <v>-637.5</v>
+      </c>
+      <c r="J422" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10">
+      <c r="A423">
+        <v>1536</v>
+      </c>
+      <c r="B423">
+        <v>9007728</v>
+      </c>
+      <c r="C423">
+        <v>146</v>
+      </c>
+      <c r="D423">
+        <v>125</v>
+      </c>
+      <c r="E423">
+        <v>86</v>
+      </c>
+      <c r="F423">
+        <v>210</v>
+      </c>
+      <c r="G423">
+        <v>372</v>
+      </c>
+      <c r="H423">
+        <v>975</v>
+      </c>
+      <c r="I423">
+        <v>603</v>
+      </c>
+      <c r="J423" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10">
+      <c r="A424">
+        <v>1748</v>
+      </c>
+      <c r="B424">
+        <v>9753880</v>
+      </c>
+      <c r="C424">
+        <v>203</v>
+      </c>
+      <c r="D424">
+        <v>189</v>
+      </c>
+      <c r="E424">
+        <v>1</v>
+      </c>
+      <c r="F424">
+        <v>189</v>
+      </c>
+      <c r="G424">
+        <v>470</v>
+      </c>
+      <c r="H424">
+        <v>-153.264</v>
+      </c>
+      <c r="I424">
+        <v>-623.263</v>
+      </c>
+      <c r="J424" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10">
+      <c r="A425">
+        <v>394</v>
+      </c>
+      <c r="B425">
+        <v>2718145</v>
+      </c>
+      <c r="C425">
+        <v>156</v>
+      </c>
+      <c r="D425">
+        <v>122</v>
+      </c>
+      <c r="E425">
+        <v>27</v>
+      </c>
+      <c r="F425">
+        <v>148</v>
+      </c>
+      <c r="G425">
+        <v>363</v>
+      </c>
+      <c r="H425">
+        <v>1522.5</v>
+      </c>
+      <c r="I425">
+        <v>1159.5</v>
+      </c>
+      <c r="J425" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10">
+      <c r="A426">
+        <v>1359</v>
+      </c>
+      <c r="B426">
+        <v>3623276</v>
+      </c>
+      <c r="C426">
+        <v>149</v>
+      </c>
+      <c r="D426">
+        <v>127</v>
+      </c>
+      <c r="E426">
+        <v>20</v>
+      </c>
+      <c r="F426">
+        <v>146</v>
+      </c>
+      <c r="G426">
+        <v>378</v>
+      </c>
+      <c r="H426">
+        <v>846.21</v>
+      </c>
+      <c r="I426">
+        <v>468.21</v>
+      </c>
+      <c r="J426" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10">
+      <c r="A427">
+        <v>541</v>
+      </c>
+      <c r="B427">
+        <v>4328373</v>
+      </c>
+      <c r="C427">
+        <v>143</v>
+      </c>
+      <c r="D427">
+        <v>132</v>
+      </c>
+      <c r="E427">
+        <v>92</v>
+      </c>
+      <c r="F427">
+        <v>223</v>
+      </c>
+      <c r="G427">
+        <v>393</v>
+      </c>
+      <c r="H427">
+        <v>1036.9</v>
+      </c>
+      <c r="I427">
+        <v>643.9</v>
+      </c>
+      <c r="J427" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10">
+      <c r="A428">
+        <v>1824</v>
+      </c>
+      <c r="B428">
+        <v>9869884</v>
+      </c>
+      <c r="C428">
+        <v>154</v>
+      </c>
+      <c r="D428">
+        <v>125</v>
+      </c>
+      <c r="E428">
+        <v>20</v>
+      </c>
+      <c r="F428">
+        <v>144</v>
+      </c>
+      <c r="G428">
+        <v>372</v>
+      </c>
+      <c r="H428">
+        <v>1738</v>
+      </c>
+      <c r="I428">
+        <v>1366</v>
+      </c>
+      <c r="J428" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10">
+      <c r="A429">
+        <v>1888</v>
+      </c>
+      <c r="B429">
+        <v>10021153</v>
+      </c>
+      <c r="C429">
+        <v>166</v>
+      </c>
+      <c r="D429">
+        <v>127</v>
+      </c>
+      <c r="E429">
+        <v>28</v>
+      </c>
+      <c r="F429">
+        <v>154</v>
+      </c>
+      <c r="G429">
+        <v>378</v>
+      </c>
+      <c r="H429">
+        <v>1685.5</v>
+      </c>
+      <c r="I429">
+        <v>1307.5</v>
+      </c>
+      <c r="J429" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10">
+      <c r="A430">
+        <v>903</v>
+      </c>
+      <c r="B430">
+        <v>8756313</v>
+      </c>
+      <c r="C430">
+        <v>148</v>
+      </c>
+      <c r="D430">
+        <v>119</v>
+      </c>
+      <c r="E430">
+        <v>92</v>
+      </c>
+      <c r="F430">
+        <v>210</v>
+      </c>
+      <c r="G430">
+        <v>354</v>
+      </c>
+      <c r="H430">
+        <v>279.5</v>
+      </c>
+      <c r="I430">
+        <v>-74.5</v>
+      </c>
+      <c r="J430" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10">
+      <c r="A431">
+        <v>1685</v>
+      </c>
+      <c r="B431">
+        <v>9645539</v>
+      </c>
+      <c r="C431">
+        <v>147</v>
+      </c>
+      <c r="D431">
+        <v>124</v>
+      </c>
+      <c r="E431">
+        <v>76</v>
+      </c>
+      <c r="F431">
+        <v>199</v>
+      </c>
+      <c r="G431">
+        <v>369</v>
+      </c>
+      <c r="H431">
+        <v>336.5</v>
+      </c>
+      <c r="I431">
+        <v>-32.5</v>
+      </c>
+      <c r="J431" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10">
+      <c r="A432">
+        <v>1887</v>
+      </c>
+      <c r="B432">
+        <v>10019743</v>
+      </c>
+      <c r="C432">
+        <v>150</v>
+      </c>
+      <c r="D432">
+        <v>133</v>
+      </c>
+      <c r="E432">
+        <v>15</v>
+      </c>
+      <c r="F432">
+        <v>147</v>
+      </c>
+      <c r="G432">
+        <v>396</v>
+      </c>
+      <c r="H432">
+        <v>-32.5</v>
+      </c>
+      <c r="I432">
+        <v>-428.5</v>
+      </c>
+      <c r="J432" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10">
+      <c r="A433">
+        <v>1224</v>
+      </c>
+      <c r="B433">
+        <v>5022767</v>
+      </c>
+      <c r="C433">
+        <v>195</v>
+      </c>
+      <c r="D433">
+        <v>181</v>
+      </c>
+      <c r="E433">
+        <v>1</v>
+      </c>
+      <c r="F433">
+        <v>181</v>
+      </c>
+      <c r="G433">
+        <v>450</v>
+      </c>
+      <c r="H433">
+        <v>-167.5</v>
+      </c>
+      <c r="I433">
+        <v>-617.5</v>
+      </c>
+      <c r="J433" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10">
+      <c r="A434">
+        <v>1903</v>
+      </c>
+      <c r="B434">
+        <v>6741423</v>
+      </c>
+      <c r="C434">
+        <v>144</v>
+      </c>
+      <c r="D434">
+        <v>123</v>
+      </c>
+      <c r="E434">
+        <v>86</v>
+      </c>
+      <c r="F434">
+        <v>208</v>
+      </c>
+      <c r="G434">
+        <v>366</v>
+      </c>
+      <c r="H434">
+        <v>709.9</v>
+      </c>
+      <c r="I434">
+        <v>343.9</v>
+      </c>
+      <c r="J434" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10">
+      <c r="A435">
+        <v>208</v>
+      </c>
+      <c r="B435">
+        <v>5208114</v>
+      </c>
+      <c r="C435">
+        <v>227</v>
+      </c>
+      <c r="D435">
+        <v>166</v>
+      </c>
+      <c r="E435">
+        <v>45</v>
+      </c>
+      <c r="F435">
+        <v>210</v>
+      </c>
+      <c r="G435">
+        <v>330</v>
+      </c>
+      <c r="H435">
+        <v>553.6</v>
+      </c>
+      <c r="I435">
+        <v>223.6</v>
+      </c>
+      <c r="J435" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10">
+      <c r="A436">
+        <v>349</v>
+      </c>
+      <c r="B436">
+        <v>5924943</v>
+      </c>
+      <c r="C436">
+        <v>333</v>
+      </c>
+      <c r="D436">
+        <v>176</v>
+      </c>
+      <c r="E436">
+        <v>138</v>
+      </c>
+      <c r="F436">
+        <v>313</v>
+      </c>
+      <c r="G436">
+        <v>350</v>
+      </c>
+      <c r="H436">
+        <v>1480</v>
+      </c>
+      <c r="I436">
+        <v>1130</v>
+      </c>
+      <c r="J436" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10">
+      <c r="A437">
+        <v>112</v>
+      </c>
+      <c r="B437">
+        <v>5021514</v>
+      </c>
+      <c r="C437">
+        <v>155</v>
+      </c>
+      <c r="D437">
+        <v>120</v>
+      </c>
+      <c r="E437">
+        <v>90</v>
+      </c>
+      <c r="F437">
+        <v>209</v>
+      </c>
+      <c r="G437">
+        <v>357</v>
+      </c>
+      <c r="H437">
+        <v>773.5</v>
+      </c>
+      <c r="I437">
+        <v>416.5</v>
+      </c>
+      <c r="J437" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10">
+      <c r="A438">
+        <v>983</v>
+      </c>
+      <c r="B438">
+        <v>8422522</v>
+      </c>
+      <c r="C438">
+        <v>167</v>
+      </c>
+      <c r="D438">
+        <v>127</v>
+      </c>
+      <c r="E438">
+        <v>26</v>
+      </c>
+      <c r="F438">
+        <v>152</v>
+      </c>
+      <c r="G438">
+        <v>378</v>
+      </c>
+      <c r="H438">
+        <v>327</v>
+      </c>
+      <c r="I438">
+        <v>-51</v>
+      </c>
+      <c r="J438" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10">
+      <c r="A439">
+        <v>1260</v>
+      </c>
+      <c r="B439">
+        <v>6742658</v>
+      </c>
+      <c r="C439">
+        <v>192</v>
+      </c>
+      <c r="D439">
+        <v>181</v>
+      </c>
+      <c r="E439">
+        <v>1</v>
+      </c>
+      <c r="F439">
+        <v>181</v>
+      </c>
+      <c r="G439">
+        <v>450</v>
+      </c>
+      <c r="H439">
+        <v>-227.5</v>
+      </c>
+      <c r="I439">
+        <v>-677.5</v>
+      </c>
+      <c r="J439" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10">
+      <c r="A440">
+        <v>1037</v>
+      </c>
+      <c r="B440">
+        <v>8244938</v>
+      </c>
+      <c r="C440">
+        <v>190</v>
+      </c>
+      <c r="D440">
+        <v>175</v>
+      </c>
+      <c r="E440">
+        <v>1</v>
+      </c>
+      <c r="F440">
+        <v>175</v>
+      </c>
+      <c r="G440">
+        <v>435</v>
+      </c>
+      <c r="H440">
+        <v>-185</v>
+      </c>
+      <c r="I440">
+        <v>-620</v>
+      </c>
+      <c r="J440" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10">
+      <c r="A441">
+        <v>1628</v>
+      </c>
+      <c r="B441">
+        <v>9545040</v>
+      </c>
+      <c r="C441">
+        <v>145</v>
+      </c>
+      <c r="D441">
+        <v>117</v>
+      </c>
+      <c r="E441">
+        <v>22</v>
+      </c>
+      <c r="F441">
+        <v>138</v>
+      </c>
+      <c r="G441">
+        <v>348</v>
+      </c>
+      <c r="H441">
+        <v>1096</v>
+      </c>
+      <c r="I441">
+        <v>748</v>
+      </c>
+      <c r="J441" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10">
+      <c r="A442">
+        <v>1851</v>
+      </c>
+      <c r="B442">
+        <v>9926692</v>
+      </c>
+      <c r="C442">
+        <v>97</v>
+      </c>
+      <c r="D442">
+        <v>73</v>
+      </c>
+      <c r="E442">
+        <v>17</v>
+      </c>
+      <c r="F442">
+        <v>89</v>
+      </c>
+      <c r="G442">
+        <v>360</v>
+      </c>
+      <c r="H442">
+        <v>733.4</v>
+      </c>
+      <c r="I442">
+        <v>373.4</v>
+      </c>
+      <c r="J442" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10">
+      <c r="A443">
+        <v>49</v>
+      </c>
+      <c r="B443">
+        <v>5463208</v>
+      </c>
+      <c r="C443">
+        <v>161</v>
+      </c>
+      <c r="D443">
+        <v>117</v>
+      </c>
+      <c r="E443">
+        <v>37</v>
+      </c>
+      <c r="F443">
+        <v>153</v>
+      </c>
+      <c r="G443">
+        <v>348</v>
+      </c>
+      <c r="H443">
+        <v>1152</v>
+      </c>
+      <c r="I443">
+        <v>804</v>
+      </c>
+      <c r="J443" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10">
+      <c r="A444">
+        <v>1718</v>
+      </c>
+      <c r="B444">
+        <v>9689853</v>
+      </c>
+      <c r="C444">
+        <v>173</v>
+      </c>
+      <c r="D444">
+        <v>118</v>
+      </c>
+      <c r="E444">
+        <v>31</v>
+      </c>
+      <c r="F444">
+        <v>148</v>
+      </c>
+      <c r="G444">
+        <v>351</v>
+      </c>
+      <c r="H444">
+        <v>156</v>
+      </c>
+      <c r="I444">
+        <v>-195</v>
+      </c>
+      <c r="J444" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10">
+      <c r="A445">
+        <v>718</v>
+      </c>
+      <c r="B445">
+        <v>6048199</v>
+      </c>
+      <c r="C445">
+        <v>168</v>
+      </c>
+      <c r="D445">
+        <v>122</v>
+      </c>
+      <c r="E445">
+        <v>32</v>
+      </c>
+      <c r="F445">
+        <v>153</v>
+      </c>
+      <c r="G445">
+        <v>363</v>
+      </c>
+      <c r="H445">
+        <v>767.5</v>
+      </c>
+      <c r="I445">
+        <v>404.5</v>
+      </c>
+      <c r="J445" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10">
+      <c r="A446">
+        <v>1743</v>
+      </c>
+      <c r="B446">
+        <v>9746592</v>
+      </c>
+      <c r="C446">
+        <v>192</v>
+      </c>
+      <c r="D446">
+        <v>172</v>
+      </c>
+      <c r="E446">
+        <v>1</v>
+      </c>
+      <c r="F446">
+        <v>172</v>
+      </c>
+      <c r="G446">
+        <v>427.5</v>
+      </c>
+      <c r="H446">
+        <v>-192.372</v>
+      </c>
+      <c r="I446">
+        <v>-619.872</v>
+      </c>
+      <c r="J446" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
